--- a/CASESTUDY_Hydrogenation.xlsx
+++ b/CASESTUDY_Hydrogenation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/lf576_cam_ac_uk/Documents/04_Coding/hydrogenation/current_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{376BE0CC-9E22-4B97-BA0E-DE8BF9F43929}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E697BDC1-13ED-4EBC-B1A3-01FB133D5D2F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Overview" sheetId="2" r:id="rId2"/>
     <sheet name="CaseStudy_Hydrogenation" sheetId="3" r:id="rId3"/>
-    <sheet name="Context_Hydrogenation_New" sheetId="4" r:id="rId4"/>
+    <sheet name="Context_Input" sheetId="4" r:id="rId4"/>
     <sheet name="Context_Compact" sheetId="5" r:id="rId5"/>
     <sheet name="Context Hydrogenation" sheetId="6" r:id="rId6"/>
   </sheets>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="492">
   <si>
     <t>This is the file containing all the information about the Hydrogenation Process Case Study</t>
   </si>
@@ -911,9 +911,6 @@
     <t>#CoolingFluidStream</t>
   </si>
   <si>
-    <t>Setze ich das flowrate profile hierhin oder an die jacket oder an den Stream (Stream dann ohne Kontext)</t>
-  </si>
-  <si>
     <t>#Jacket_Structure</t>
   </si>
   <si>
@@ -968,9 +965,6 @@
     <t>Wenn ich den Space der Phase mit dem MaterialVolume beschreibe, brauche ich dann überhaupt die Vessel noch? Weil dann wissen wir ja MaterialVolume Reactor locatedIn Vessel</t>
   </si>
   <si>
-    <t>Die Initial Mass Fractions hier oder in die Molekül Contexts</t>
-  </si>
-  <si>
     <t>#LiquidPhase</t>
   </si>
   <si>
@@ -1524,13 +1518,37 @@
   </si>
   <si>
     <t>#H4</t>
+  </si>
+  <si>
+    <t>In Context_Input können die Devices, Phases und Molecules eingefügt werden, und dann kann man direkt deren Kontext beschreiben</t>
+  </si>
+  <si>
+    <t>Daraufhin wird automatisch der kompakte Kontext in Context_Compact erstellt</t>
+  </si>
+  <si>
+    <t>Diesen kann man dann rauskopieren in die Excel context_connections.xlsx</t>
+  </si>
+  <si>
+    <t>Wenn man dann  python create_context_connections.py aufruft, erstellt es einem automatisch die entsprechenden Connections mit den Properties, die dann in das RO-Crate eingefügt werden können</t>
+  </si>
+  <si>
+    <t>Für das Einfügen habe ich bis jetzt noch keine Automatisierungsschritt erstellt.</t>
+  </si>
+  <si>
+    <t>#InitialMassFraction_Water_LiquidPhase in Liquid Phase</t>
+  </si>
+  <si>
+    <t>#SetFlowrateProfile_Jacket in Jacket</t>
+  </si>
+  <si>
+    <t>Reactor Energy würde ich prinzipiell nicht wirklich hiermit verbinden, aber da ich definiert habe dass MassFlowMeter ein Teil von Reactor ist muss ich das der Vollständigkeit halber auch hier aufführen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1554,6 +1572,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1627,7 +1651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1649,6 +1673,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1983,12 +2008,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D6EF24-A5F2-4E49-9641-E94D8B75807A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -3713,7 +3763,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B1" t="s">
         <v>243</v>
@@ -3734,13 +3784,13 @@
         <v>233</v>
       </c>
       <c r="H1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -3754,74 +3804,74 @@
     </row>
     <row r="4" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" t="s">
         <v>362</v>
       </c>
-      <c r="B6" t="s">
-        <v>365</v>
-      </c>
-      <c r="C6" t="s">
-        <v>364</v>
-      </c>
       <c r="D6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3831,7 +3881,7 @@
     <row r="14" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>90</v>
@@ -3839,48 +3889,48 @@
     </row>
     <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B16" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3903,61 +3953,61 @@
     </row>
     <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B30" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H30" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H31" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H32" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H34" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H35" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3975,51 +4025,51 @@
     </row>
     <row r="42" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C42" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D42" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H42" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H43" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H44" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H45" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H46" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4039,51 +4089,51 @@
     </row>
     <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C55" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D55" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H55" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C56" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H56" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H57" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="58" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H58" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="59" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H59" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4095,7 +4145,7 @@
     <row r="66" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>90</v>
@@ -4103,51 +4153,51 @@
     </row>
     <row r="68" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B68" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C68" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H68" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B69" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H69" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="70" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H70" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H71" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H72" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4159,7 +4209,7 @@
     <row r="79" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>90</v>
@@ -4167,51 +4217,51 @@
     </row>
     <row r="81" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C81" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H81" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B82" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C82" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D82" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H82" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="83" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H83" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="84" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H84" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H85" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4223,7 +4273,7 @@
     <row r="92" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>90</v>
@@ -4231,51 +4281,54 @@
     </row>
     <row r="94" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B94" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H94" t="s">
-        <v>315</v>
+        <v>313</v>
+      </c>
+      <c r="I94" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="95" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B95" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C95" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D95" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H95" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="96" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H96" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="97" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H97" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="98" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H98" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4287,7 +4340,7 @@
     <row r="105" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="106" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>90</v>
@@ -4295,42 +4348,42 @@
     </row>
     <row r="107" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B107" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D107" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H107" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="108" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B108" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H108" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="109" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="110" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H110" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="111" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H111" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4354,27 +4407,27 @@
     </row>
     <row r="124" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C124" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G124" t="s">
         <v>261</v>
       </c>
       <c r="I124" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="125" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E125" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G125" t="s">
         <v>266</v>
@@ -4382,21 +4435,18 @@
     </row>
     <row r="126" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E126" t="s">
-        <v>288</v>
-      </c>
-      <c r="I126" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="127" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E127" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="128" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4417,32 +4467,32 @@
     </row>
     <row r="137" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C137" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E137" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G137" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="138" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="139" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E139" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="140" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4464,29 +4514,29 @@
     </row>
     <row r="150" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C150" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E150" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="151" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E151" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E152" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="153" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4508,29 +4558,29 @@
     </row>
     <row r="163" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C163" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E163" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E164" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="165" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E165" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="166" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4544,7 +4594,7 @@
     <row r="174" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="175" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J175" s="13" t="s">
         <v>89</v>
@@ -4552,29 +4602,29 @@
     </row>
     <row r="176" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C176" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E176" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="177" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E177" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="178" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E178" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="179" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4588,7 +4638,7 @@
     <row r="187" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="188" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J188" s="13" t="s">
         <v>89</v>
@@ -4596,32 +4646,29 @@
     </row>
     <row r="189" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C189" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E189" t="s">
-        <v>284</v>
+        <v>283</v>
+      </c>
+      <c r="I189" s="15" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="190" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>286</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E190" t="s">
-        <v>282</v>
-      </c>
-      <c r="I190" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="191" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E191" t="s">
         <v>280</v>
@@ -4725,7 +4772,7 @@
     </row>
     <row r="232" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C232" t="s">
         <v>269</v>
@@ -4733,7 +4780,7 @@
     </row>
     <row r="233" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C233" t="s">
         <v>268</v>
@@ -4766,12 +4813,11 @@
       <c r="E244" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="E245" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
+      <c r="I244" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="246" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="247" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="248" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4800,12 +4846,11 @@
       <c r="E257" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="E258" s="7" t="s">
+      <c r="I257" s="15" t="s">
         <v>261</v>
       </c>
     </row>
+    <row r="258" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="259" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="260" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="261" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -5021,9 +5066,9 @@
     <row r="366" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="367" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="368" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="369" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="370" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="371" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="369" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="370" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="371" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="372" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="373" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="374" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -5040,7 +5085,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B1" t="s">
         <v>243</v>
@@ -5063,7 +5108,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:G11">Context_Hydrogenation_New!A4:G13</f>
+        <f t="array" ref="A2:G11">Context_Input!A4:G13</f>
         <v>#Reactor</v>
       </c>
       <c r="B2" t="str">
@@ -5294,7 +5339,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="str" cm="1">
-        <f t="array" ref="A12:G22">Context_Hydrogenation_New!A16:G26</f>
+        <f t="array" ref="A12:G22">Context_Input!A16:G26</f>
         <v>#Vessel</v>
       </c>
       <c r="B12" t="str">
@@ -5548,7 +5593,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="str" cm="1">
-        <f t="array" ref="A23:G33">Context_Hydrogenation_New!A29:G39</f>
+        <f t="array" ref="A23:G33">Context_Input!A29:G39</f>
         <v>#Stirrer</v>
       </c>
       <c r="B23" t="str">
@@ -5802,7 +5847,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="str" cm="1">
-        <f t="array" ref="A34:G44">Context_Hydrogenation_New!A42:G52</f>
+        <f t="array" ref="A34:G44">Context_Input!A42:G52</f>
         <v>#Sparger</v>
       </c>
       <c r="B34" t="str">
@@ -6056,7 +6101,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="str" cm="1">
-        <f t="array" ref="A45:G55">Context_Hydrogenation_New!A55:G65</f>
+        <f t="array" ref="A45:G55">Context_Input!A55:G65</f>
         <v>#Jacket</v>
       </c>
       <c r="B45" t="str">
@@ -6310,7 +6355,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="str" cm="1">
-        <f t="array" ref="A56:G66">Context_Hydrogenation_New!A68:G78</f>
+        <f t="array" ref="A56:G66">Context_Input!A68:G78</f>
         <v>#TemperatureSensor</v>
       </c>
       <c r="B56" t="str">
@@ -6564,7 +6609,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="str" cm="1">
-        <f t="array" ref="A67:G77">Context_Hydrogenation_New!A81:G91</f>
+        <f t="array" ref="A67:G77">Context_Input!A81:G91</f>
         <v>#PressureSensor</v>
       </c>
       <c r="B67" t="str">
@@ -6818,7 +6863,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="str" cm="1">
-        <f t="array" ref="A78:G88">Context_Hydrogenation_New!A94:G104</f>
+        <f t="array" ref="A78:G88">Context_Input!A94:G104</f>
         <v>#MassFlowMeter</v>
       </c>
       <c r="B78" t="str">
@@ -7072,7 +7117,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="str" cm="1">
-        <f t="array" ref="A89:G100">Context_Hydrogenation_New!A107:G118</f>
+        <f t="array" ref="A89:G100">Context_Input!A107:G118</f>
         <v>#Balance</v>
       </c>
       <c r="B89" t="str">
@@ -7349,7 +7394,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="str" cm="1">
-        <f t="array" ref="A101:G111">Context_Hydrogenation_New!A124:G134</f>
+        <f t="array" ref="A101:G111">Context_Input!A124:G134</f>
         <v>#LiquidPhase</v>
       </c>
       <c r="B101">
@@ -7603,7 +7648,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="str" cm="1">
-        <f t="array" ref="A112:G122">Context_Hydrogenation_New!A137:G147</f>
+        <f t="array" ref="A112:G122">Context_Input!A137:G147</f>
         <v>#SolidPhase</v>
       </c>
       <c r="B112">
@@ -7857,7 +7902,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="str" cm="1">
-        <f t="array" ref="A123:G133">Context_Hydrogenation_New!A150:G160</f>
+        <f t="array" ref="A123:G133">Context_Input!A150:G160</f>
         <v>#CatalystPhase</v>
       </c>
       <c r="B123">
@@ -8111,7 +8156,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="str" cm="1">
-        <f t="array" ref="A134:G144">Context_Hydrogenation_New!A163:G173</f>
+        <f t="array" ref="A134:G144">Context_Input!A163:G173</f>
         <v>#GasPhase</v>
       </c>
       <c r="B134">
@@ -8365,7 +8410,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="str" cm="1">
-        <f t="array" ref="A145:G155">Context_Hydrogenation_New!A176:G186</f>
+        <f t="array" ref="A145:G155">Context_Input!A176:G186</f>
         <v>#DispersedGasPhase</v>
       </c>
       <c r="B145">
@@ -8619,7 +8664,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="str" cm="1">
-        <f t="array" ref="A156:G166">Context_Hydrogenation_New!A189:G199</f>
+        <f t="array" ref="A156:G166">Context_Input!A189:G199</f>
         <v>#CoolingFluidPhase</v>
       </c>
       <c r="B156">
@@ -8648,8 +8693,8 @@
       <c r="B157">
         <v>0</v>
       </c>
-      <c r="C157" t="str">
-        <v>#SetFlowrateProfile_Jacket</v>
+      <c r="C157">
+        <v>0</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -8873,7 +8918,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="str" cm="1">
-        <f t="array" ref="A167:G177">Context_Hydrogenation_New!A202:G212</f>
+        <f t="array" ref="A167:G177">Context_Input!A202:G212</f>
         <v>#HydrogenSpargerPhase</v>
       </c>
       <c r="B167">
@@ -9127,7 +9172,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="str" cm="1">
-        <f t="array" ref="A178:G188">Context_Hydrogenation_New!A215:G225</f>
+        <f t="array" ref="A178:G188">Context_Input!A215:G225</f>
         <v>#CleaningFluidPhase</v>
       </c>
       <c r="B178">
@@ -9381,7 +9426,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="str" cm="1">
-        <f t="array" ref="A189:G199">Context_Hydrogenation_New!A231:G241</f>
+        <f t="array" ref="A189:G199">Context_Input!A231:G241</f>
         <v>#H2</v>
       </c>
       <c r="B189">
@@ -9635,7 +9680,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="str" cm="1">
-        <f t="array" ref="A200:G210">Context_Hydrogenation_New!A244:G254</f>
+        <f t="array" ref="A200:G210">Context_Input!A244:G254</f>
         <v>#H2O</v>
       </c>
       <c r="B200">
@@ -9670,8 +9715,8 @@
       <c r="D201">
         <v>0</v>
       </c>
-      <c r="E201" t="str">
-        <v>#InitialMassFraction_Water_LiquidPhase</v>
+      <c r="E201">
+        <v>0</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -9889,7 +9934,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="str" cm="1">
-        <f t="array" ref="A211:G221">Context_Hydrogenation_New!A257:G267</f>
+        <f t="array" ref="A211:G221">Context_Input!A257:G267</f>
         <v>#Solvent</v>
       </c>
       <c r="B211">
@@ -9924,8 +9969,8 @@
       <c r="D212">
         <v>0</v>
       </c>
-      <c r="E212" t="str">
-        <v>#InitialMassFraction_Solvent_LiquidPhase</v>
+      <c r="E212">
+        <v>0</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -10143,7 +10188,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="str" cm="1">
-        <f t="array" ref="A222:G232">Context_Hydrogenation_New!A270:G280</f>
+        <f t="array" ref="A222:G232">Context_Input!A270:G280</f>
         <v>#RDY</v>
       </c>
       <c r="B222">
@@ -10397,7 +10442,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" cm="1">
-        <f t="array" ref="A233:G243">Context_Hydrogenation_New!A283:G293</f>
+        <f t="array" ref="A233:G243">Context_Input!A283:G293</f>
         <v>0</v>
       </c>
       <c r="B233">
@@ -10651,7 +10696,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" cm="1">
-        <f t="array" ref="A244:G254">Context_Hydrogenation_New!A296:G306</f>
+        <f t="array" ref="A244:G254">Context_Input!A296:G306</f>
         <v>0</v>
       </c>
       <c r="B244">
@@ -10905,7 +10950,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" cm="1">
-        <f t="array" ref="A255:G265">Context_Hydrogenation_New!A309:G319</f>
+        <f t="array" ref="A255:G265">Context_Input!A309:G319</f>
         <v>0</v>
       </c>
       <c r="B255">
@@ -11159,7 +11204,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="str" cm="1">
-        <f t="array" ref="A266:G276">Context_Hydrogenation_New!A322:G332</f>
+        <f t="array" ref="A266:G276">Context_Input!A322:G332</f>
         <v>#RDEt</v>
       </c>
       <c r="B266">
@@ -11413,7 +11458,7 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="str" cm="1">
-        <f t="array" ref="A277:G287">Context_Hydrogenation_New!A335:G345</f>
+        <f t="array" ref="A277:G287">Context_Input!A335:G345</f>
         <v>#Dimer1</v>
       </c>
       <c r="B277">
@@ -11667,7 +11712,7 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" t="str" cm="1">
-        <f t="array" ref="A288:G298">Context_Hydrogenation_New!A348:G358</f>
+        <f t="array" ref="A288:G298">Context_Input!A348:G358</f>
         <v>#Dimer2</v>
       </c>
       <c r="B288">
@@ -11921,7 +11966,7 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" t="str" cm="1">
-        <f t="array" ref="A299:G309">Context_Hydrogenation_New!A361:G371</f>
+        <f t="array" ref="A299:G309">Context_Input!A361:G371</f>
         <v>#Pt</v>
       </c>
       <c r="B299">
@@ -12193,47 +12238,47 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
@@ -12241,16 +12286,16 @@
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>90</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Q5" t="s">
         <v>243</v>
@@ -12258,22 +12303,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="L6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q6" t="s">
         <v>241</v>
@@ -12281,22 +12326,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B7" t="s">
+        <v>464</v>
+      </c>
+      <c r="E7" t="s">
+        <v>463</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="L7" t="s">
         <v>461</v>
       </c>
-      <c r="B7" t="s">
-        <v>466</v>
-      </c>
-      <c r="E7" t="s">
-        <v>465</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>464</v>
-      </c>
-      <c r="L7" t="s">
-        <v>463</v>
-      </c>
       <c r="M7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Q7" t="s">
         <v>239</v>
@@ -12304,25 +12349,25 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E8" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q8" t="s">
         <v>237</v>
@@ -12333,13 +12378,13 @@
         <v>250</v>
       </c>
       <c r="B9" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Q9" t="s">
         <v>235</v>
@@ -12347,16 +12392,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M10" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q10" t="s">
         <v>233</v>
@@ -12367,10 +12412,10 @@
         <v>258</v>
       </c>
       <c r="B11" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M11" t="s">
         <v>241</v>
@@ -12381,7 +12426,7 @@
         <v>261</v>
       </c>
       <c r="B12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>89</v>
@@ -12392,7 +12437,7 @@
         <v>266</v>
       </c>
       <c r="B13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>248</v>
@@ -12400,141 +12445,141 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="O14" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B15" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E15" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N15" t="s">
         <v>243</v>
       </c>
       <c r="O15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B16" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B17" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="M17" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B18" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E18" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="M18" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N18" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N19" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="O19" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M21" t="s">
         <v>233</v>
@@ -12542,19 +12587,19 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B22" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L22" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="M22" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N22" t="s">
         <v>239</v>
@@ -12562,223 +12607,223 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B24" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E24" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E25" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B26" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E26" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B27" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E27" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E28" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B29" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B30" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B31" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B33" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B34" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E34" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B35" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B37" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E37" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/CASESTUDY_Hydrogenation.xlsx
+++ b/CASESTUDY_Hydrogenation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/lf576_cam_ac_uk/Documents/04_Coding/hydrogenation/current_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E697BDC1-13ED-4EBC-B1A3-01FB133D5D2F}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F8180BA-4D06-4597-B6A5-06D2096C39F6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -1639,9 +1639,18 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -1651,7 +1660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1670,10 +1679,17 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2009,34 +2025,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D6EF24-A5F2-4E49-9641-E94D8B75807A}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>488</v>
       </c>
@@ -2050,22 +2066,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A819942F-56E1-4F4B-AB2B-0557B5EACCFB}">
   <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1:E64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="52.109375" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -2082,7 +2098,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -2099,7 +2115,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -2113,7 +2129,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>10</v>
       </c>
@@ -2127,7 +2143,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -2141,7 +2157,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>78</v>
       </c>
@@ -2149,32 +2165,32 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D11" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
         <v>77</v>
       </c>
@@ -2182,33 +2198,33 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>76</v>
       </c>
@@ -2222,7 +2238,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>72</v>
       </c>
@@ -2233,7 +2249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>69</v>
       </c>
@@ -2244,7 +2260,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>66</v>
       </c>
@@ -2255,7 +2271,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>63</v>
       </c>
@@ -2263,7 +2279,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>61</v>
       </c>
@@ -2271,32 +2287,32 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>55</v>
       </c>
@@ -2313,7 +2329,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -2324,7 +2340,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -2335,7 +2351,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -2346,7 +2362,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2357,7 +2373,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2368,7 +2384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2379,7 +2395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>36</v>
       </c>
@@ -2390,7 +2406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2401,7 +2417,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
@@ -2412,7 +2428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>30</v>
       </c>
@@ -2423,7 +2439,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>28</v>
       </c>
@@ -2434,7 +2450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>26</v>
       </c>
@@ -2445,7 +2461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>24</v>
       </c>
@@ -2456,7 +2472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -2467,7 +2483,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>18</v>
       </c>
@@ -2478,7 +2494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -2486,14 +2502,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -2504,17 +2520,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>8</v>
       </c>
@@ -2525,7 +2541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -2533,7 +2549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -2553,22 +2569,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF69EE7-86F4-48C0-B75B-749BFC7A4C35}">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1:N87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
-    <col min="11" max="11" width="33.85546875" customWidth="1"/>
-    <col min="12" max="12" width="30.5703125" customWidth="1"/>
-    <col min="13" max="13" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" customWidth="1"/>
+    <col min="7" max="7" width="23.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" customWidth="1"/>
+    <col min="11" max="11" width="33.88671875" customWidth="1"/>
+    <col min="12" max="12" width="30.5546875" customWidth="1"/>
+    <col min="13" max="13" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -2612,8 +2628,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
@@ -2654,7 +2670,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" t="s">
         <v>185</v>
@@ -2681,7 +2697,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="4"/>
       <c r="C5" t="s">
         <v>222</v>
@@ -2696,7 +2712,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
       <c r="C6" t="s">
         <v>137</v>
@@ -2711,7 +2727,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="4"/>
       <c r="C7" t="s">
         <v>123</v>
@@ -2726,7 +2742,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="7" t="s">
         <v>219</v>
@@ -2741,7 +2757,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="7" t="s">
         <v>189</v>
@@ -2750,19 +2766,19 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B11" s="4"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
     </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>216</v>
       </c>
@@ -2803,7 +2819,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15" s="4"/>
       <c r="E15" t="s">
         <v>208</v>
@@ -2830,7 +2846,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B16" s="4"/>
       <c r="C16" t="s">
         <v>123</v>
@@ -2857,7 +2873,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="4"/>
       <c r="C17" t="s">
         <v>189</v>
@@ -2872,22 +2888,22 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="4"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>199</v>
       </c>
@@ -2928,7 +2944,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="4"/>
       <c r="C24" t="s">
         <v>137</v>
@@ -2955,7 +2971,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B25" s="4"/>
       <c r="C25" t="s">
         <v>123</v>
@@ -2976,7 +2992,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" s="4"/>
       <c r="C26" t="s">
         <v>189</v>
@@ -2997,16 +3013,16 @@
         <v>167</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" s="4"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>186</v>
       </c>
@@ -3047,7 +3063,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B31" s="4"/>
       <c r="C31" t="s">
         <v>137</v>
@@ -3068,7 +3084,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B32" s="4"/>
       <c r="C32" t="s">
         <v>123</v>
@@ -3089,7 +3105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B33" s="4"/>
       <c r="E33" t="s">
         <v>170</v>
@@ -3104,16 +3120,16 @@
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" s="4"/>
     </row>
-    <row r="36" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>5</v>
       </c>
@@ -3148,7 +3164,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B38" s="4"/>
       <c r="C38" t="s">
         <v>114</v>
@@ -3181,7 +3197,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B39" s="4"/>
       <c r="C39" t="s">
         <v>109</v>
@@ -3214,7 +3230,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B40" s="4"/>
       <c r="C40" s="7" t="s">
         <v>103</v>
@@ -3236,7 +3252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B41" s="4"/>
       <c r="C41" s="7" t="s">
         <v>101</v>
@@ -3252,7 +3268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B42" s="4"/>
       <c r="C42" s="6" t="s">
         <v>123</v>
@@ -3268,7 +3284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B43" s="4"/>
       <c r="E43" s="5"/>
       <c r="M43" t="s">
@@ -3278,7 +3294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B44" s="4"/>
       <c r="E44" s="5"/>
       <c r="M44" t="s">
@@ -3288,17 +3304,17 @@
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B45" s="4"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B46" s="4"/>
     </row>
-    <row r="47" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>150</v>
       </c>
@@ -3333,7 +3349,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B49" s="4"/>
       <c r="C49" t="s">
         <v>114</v>
@@ -3360,7 +3376,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B50" s="4"/>
       <c r="C50" t="s">
         <v>109</v>
@@ -3387,21 +3403,21 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B51" s="4"/>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B52" s="4"/>
       <c r="C52" t="s">
         <v>101</v>
       </c>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B53" s="4"/>
       <c r="C53" s="6" t="s">
         <v>123</v>
@@ -3411,13 +3427,13 @@
       </c>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B54" s="4"/>
     </row>
-    <row r="55" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>143</v>
       </c>
@@ -3452,7 +3468,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B57" s="4"/>
       <c r="C57" t="s">
         <v>114</v>
@@ -3485,7 +3501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B58" s="4"/>
       <c r="C58" t="s">
         <v>109</v>
@@ -3512,7 +3528,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
         <v>103</v>
@@ -3531,14 +3547,14 @@
         <v>124</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B60" s="4"/>
       <c r="C60" s="7" t="s">
         <v>101</v>
       </c>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B61" s="4"/>
       <c r="C61" s="6" t="s">
         <v>123</v>
@@ -3548,17 +3564,17 @@
       </c>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B62" s="4"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B63" s="4"/>
     </row>
-    <row r="64" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>121</v>
       </c>
@@ -3587,7 +3603,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B66" s="4"/>
       <c r="C66" t="s">
         <v>114</v>
@@ -3614,7 +3630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B67" s="4"/>
       <c r="C67" t="s">
         <v>109</v>
@@ -3635,7 +3651,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B68" s="4"/>
       <c r="C68" t="s">
         <v>103</v>
@@ -3645,65 +3661,65 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
       <c r="C69" t="s">
         <v>101</v>
       </c>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B70" s="4"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B71" s="4"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B72" s="4"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B74" s="4"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B75" s="4"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B76" s="4"/>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B77" s="4"/>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B78" s="4"/>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B79" s="4"/>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B80" s="4"/>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B81" s="4"/>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B82" s="4"/>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B83" s="4"/>
     </row>
-    <row r="84" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>18</v>
       </c>
@@ -3732,12 +3748,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
         <v>92</v>
       </c>
@@ -3749,19 +3765,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D5FB7C-FC33-457D-B6B0-7F2ECBB63948}">
-  <dimension ref="A1:K374"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J374"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="51.5703125" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="16" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>374</v>
       </c>
@@ -3783,7 +3799,7 @@
       <c r="G1" t="s">
         <v>233</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="16" t="s">
         <v>373</v>
       </c>
       <c r="I1" t="s">
@@ -3793,16 +3809,19 @@
         <v>371</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>86</v>
       </c>
+      <c r="H3" s="18"/>
       <c r="J3" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>360</v>
       </c>
@@ -3815,11 +3834,11 @@
       <c r="D4" t="s">
         <v>368</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="16" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="5" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>360</v>
       </c>
@@ -3832,11 +3851,11 @@
       <c r="D5" t="s">
         <v>364</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>360</v>
       </c>
@@ -3849,45 +3868,48 @@
       <c r="D6" t="s">
         <v>361</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>360</v>
       </c>
       <c r="C7" t="s">
         <v>359</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H8" t="s">
+    <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H8" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H9" t="s">
+    <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="16" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>357</v>
       </c>
+      <c r="H15" s="18"/>
       <c r="J15" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>356</v>
       </c>
@@ -3900,11 +3922,11 @@
       <c r="D16" t="s">
         <v>354</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="16" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>356</v>
       </c>
@@ -3914,44 +3936,46 @@
       <c r="D17" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H18" t="s">
+    <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="19" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H19" t="s">
+    <row r="19" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H20" t="s">
+    <row r="20" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="18" t="s">
         <v>77</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>351</v>
       </c>
@@ -3964,11 +3988,11 @@
       <c r="D29" t="s">
         <v>349</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="16" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>351</v>
       </c>
@@ -3981,49 +4005,52 @@
       <c r="D30" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H31" t="s">
+    <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H31" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="32" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H32" t="s">
+    <row r="32" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="33" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H33" t="s">
+    <row r="33" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H34" t="s">
+    <row r="34" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="16" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="35" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H35" t="s">
+    <row r="35" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="16" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="36" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="17"/>
+    </row>
+    <row r="41" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="H41" s="18"/>
       <c r="J41" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>343</v>
       </c>
@@ -4036,11 +4063,11 @@
       <c r="D42" t="s">
         <v>341</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="16" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="43" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>343</v>
       </c>
@@ -4053,41 +4080,44 @@
       <c r="D43" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="44" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H44" t="s">
+    <row r="44" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H44" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H45" t="s">
+    <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H46" t="s">
+    <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H46" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="17"/>
+    </row>
+    <row r="54" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="H54" s="18"/>
       <c r="J54" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>337</v>
       </c>
@@ -4100,11 +4130,11 @@
       <c r="D55" t="s">
         <v>335</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="16" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>337</v>
       </c>
@@ -4117,41 +4147,44 @@
       <c r="D56" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H57" t="s">
+    <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="58" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H58" t="s">
+    <row r="58" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H58" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="59" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H59" t="s">
+    <row r="59" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H59" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H66" s="17"/>
+    </row>
+    <row r="67" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>332</v>
       </c>
+      <c r="H67" s="18"/>
       <c r="J67" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>331</v>
       </c>
@@ -4164,11 +4197,11 @@
       <c r="D68" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="16" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="69" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>331</v>
       </c>
@@ -4181,41 +4214,44 @@
       <c r="D69" t="s">
         <v>326</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="70" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H70" t="s">
+    <row r="70" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H70" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H71" t="s">
+    <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H71" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H72" t="s">
+    <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H72" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H79" s="17"/>
+    </row>
+    <row r="80" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>325</v>
       </c>
+      <c r="H80" s="18"/>
       <c r="J80" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>324</v>
       </c>
@@ -4228,11 +4264,11 @@
       <c r="D81" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="16" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="82" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>324</v>
       </c>
@@ -4245,41 +4281,44 @@
       <c r="D82" t="s">
         <v>319</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="83" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H83" t="s">
+    <row r="83" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H83" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="84" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H84" t="s">
+    <row r="84" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H84" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="85" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H85" t="s">
+    <row r="85" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="86" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H92" s="17"/>
+    </row>
+    <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>318</v>
       </c>
+      <c r="H93" s="18"/>
       <c r="J93" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>317</v>
       </c>
@@ -4292,14 +4331,14 @@
       <c r="D94" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="16" t="s">
         <v>313</v>
       </c>
       <c r="I94" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="95" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>317</v>
       </c>
@@ -4312,41 +4351,44 @@
       <c r="D95" t="s">
         <v>310</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="96" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H96" t="s">
+    <row r="96" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H96" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="97" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H97" t="s">
+    <row r="97" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H97" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="98" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H98" t="s">
+    <row r="98" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H98" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="101" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H105" s="17"/>
+    </row>
+    <row r="106" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>309</v>
       </c>
+      <c r="H106" s="18"/>
       <c r="J106" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="107" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>308</v>
       </c>
@@ -4356,56 +4398,65 @@
       <c r="D107" t="s">
         <v>306</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="16" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>308</v>
       </c>
       <c r="B108" t="s">
         <v>304</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="109" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H109" t="s">
+    <row r="109" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H109" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="110" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H110" t="s">
+    <row r="110" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H110" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="111" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="H111" t="s">
+    <row r="111" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="H111" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="112" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="113" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="115" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="116" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="117" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="118" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="119" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H119" s="19"/>
+    </row>
+    <row r="120" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H120" s="19"/>
+    </row>
+    <row r="121" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H121" s="19"/>
+    </row>
+    <row r="122" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H122" s="19"/>
+    </row>
+    <row r="123" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>85</v>
       </c>
+      <c r="H123" s="20"/>
       <c r="J123" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>299</v>
       </c>
@@ -4422,7 +4473,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="125" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>299</v>
       </c>
@@ -4433,7 +4484,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="126" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>299</v>
       </c>
@@ -4441,7 +4492,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="127" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>299</v>
       </c>
@@ -4449,23 +4500,26 @@
         <v>297</v>
       </c>
     </row>
-    <row r="128" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="129" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="130" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="131" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="132" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="133" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="134" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="135" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H135" s="17"/>
+    </row>
+    <row r="136" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="13" t="s">
         <v>80</v>
       </c>
+      <c r="H136" s="20"/>
       <c r="J136" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="137" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>296</v>
       </c>
@@ -4479,7 +4533,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="138" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>296</v>
       </c>
@@ -4487,7 +4541,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="139" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>296</v>
       </c>
@@ -4495,24 +4549,27 @@
         <v>287</v>
       </c>
     </row>
-    <row r="140" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="141" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="142" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="143" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="144" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="145" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="147" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="148" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H148" s="17"/>
+    </row>
+    <row r="149" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="s">
         <v>78</v>
       </c>
+      <c r="H149" s="20"/>
       <c r="J149" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>294</v>
       </c>
@@ -4523,7 +4580,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="151" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>294</v>
       </c>
@@ -4531,7 +4588,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="152" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>294</v>
       </c>
@@ -4539,24 +4596,27 @@
         <v>287</v>
       </c>
     </row>
-    <row r="153" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="154" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="155" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="157" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="158" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="159" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="160" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="161" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H161" s="17"/>
+    </row>
+    <row r="162" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="13" t="s">
         <v>83</v>
       </c>
+      <c r="H162" s="20"/>
       <c r="J162" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="163" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>293</v>
       </c>
@@ -4567,7 +4627,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="164" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>293</v>
       </c>
@@ -4575,7 +4635,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="165" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>293</v>
       </c>
@@ -4583,24 +4643,27 @@
         <v>287</v>
       </c>
     </row>
-    <row r="166" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="167" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="168" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="169" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="170" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="171" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="172" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="174" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H174" s="17"/>
+    </row>
+    <row r="175" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="13" t="s">
         <v>292</v>
       </c>
+      <c r="H175" s="20"/>
       <c r="J175" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="176" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>291</v>
       </c>
@@ -4611,7 +4674,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="177" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>291</v>
       </c>
@@ -4619,7 +4682,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="178" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>291</v>
       </c>
@@ -4627,24 +4690,27 @@
         <v>287</v>
       </c>
     </row>
-    <row r="179" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="180" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="181" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="182" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="183" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="184" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="185" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="187" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H187" s="17"/>
+    </row>
+    <row r="188" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A188" s="13" t="s">
         <v>286</v>
       </c>
+      <c r="H188" s="20"/>
       <c r="J188" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="189" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>285</v>
       </c>
@@ -4654,11 +4720,11 @@
       <c r="E189" t="s">
         <v>283</v>
       </c>
-      <c r="I189" s="15" t="s">
+      <c r="I189" s="14" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="190" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>285</v>
       </c>
@@ -4666,7 +4732,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="191" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>285</v>
       </c>
@@ -4674,24 +4740,27 @@
         <v>280</v>
       </c>
     </row>
-    <row r="192" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="193" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="194" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="195" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="196" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="197" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="198" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="199" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="200" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H200" s="17"/>
+    </row>
+    <row r="201" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="13" t="s">
         <v>279</v>
       </c>
+      <c r="H201" s="20"/>
       <c r="J201" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="202" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>278</v>
       </c>
@@ -4702,7 +4771,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="203" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>278</v>
       </c>
@@ -4710,7 +4779,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="204" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>278</v>
       </c>
@@ -4718,51 +4787,63 @@
         <v>274</v>
       </c>
     </row>
-    <row r="205" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="206" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="207" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="208" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="209" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="210" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="211" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="212" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="213" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H213" s="17"/>
+    </row>
+    <row r="214" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="13" t="s">
         <v>273</v>
       </c>
+      <c r="H214" s="20"/>
       <c r="J214" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="215" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="216" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="217" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="218" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="219" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="220" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="221" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="222" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="223" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="224" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="225" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="226" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H226" s="19"/>
+    </row>
+    <row r="227" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H227" s="19"/>
+    </row>
+    <row r="228" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H228" s="19"/>
+    </row>
+    <row r="229" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H229" s="19"/>
+    </row>
+    <row r="230" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A230" s="10" t="s">
         <v>271</v>
       </c>
+      <c r="H230" s="21"/>
       <c r="J230" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="231" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>115</v>
       </c>
@@ -4770,7 +4851,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="232" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>482</v>
       </c>
@@ -4778,7 +4859,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="233" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>483</v>
       </c>
@@ -4786,24 +4867,27 @@
         <v>268</v>
       </c>
     </row>
-    <row r="234" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="235" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="236" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="237" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="238" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="239" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="240" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="241" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="242" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H242" s="17"/>
+    </row>
+    <row r="243" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A243" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="H243" s="21"/>
       <c r="J243" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="244" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>267</v>
       </c>
@@ -4813,30 +4897,33 @@
       <c r="E244" t="s">
         <v>262</v>
       </c>
-      <c r="I244" s="15" t="s">
+      <c r="I244" s="14" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="245" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="246" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="247" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="248" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="249" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="250" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="251" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="252" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="253" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="254" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H255" s="17"/>
+    </row>
+    <row r="256" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A256" s="10" t="s">
         <v>265</v>
       </c>
+      <c r="H256" s="21"/>
       <c r="J256" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="257" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>264</v>
       </c>
@@ -4846,30 +4933,33 @@
       <c r="E257" t="s">
         <v>262</v>
       </c>
-      <c r="I257" s="15" t="s">
+      <c r="I257" s="14" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="258" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="265" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="266" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="267" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="268" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="269" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="259" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="260" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="261" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="262" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="263" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="264" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="265" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="266" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="267" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="268" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H268" s="17"/>
+    </row>
+    <row r="269" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A269" s="10" t="s">
         <v>40</v>
       </c>
+      <c r="H269" s="21"/>
       <c r="J269" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="270" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>146</v>
       </c>
@@ -4877,7 +4967,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="271" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>146</v>
       </c>
@@ -4885,7 +4975,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="272" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>146</v>
       </c>
@@ -4893,84 +4983,96 @@
         <v>258</v>
       </c>
     </row>
-    <row r="273" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="274" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="275" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="276" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="277" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="278" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="279" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="280" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="281" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="282" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="274" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="275" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="276" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="277" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="278" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="279" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="280" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="281" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H281" s="17"/>
+    </row>
+    <row r="282" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A282" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="H282" s="21"/>
       <c r="J282" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="284" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="289" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="290" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="291" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="292" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="293" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="294" spans="1:10" s="11" customFormat="1" collapsed="1" x14ac:dyDescent="0.25"/>
-    <row r="295" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="284" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="285" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="286" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="287" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="288" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="289" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="290" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="291" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="292" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="293" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="294" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H294" s="17"/>
+    </row>
+    <row r="295" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A295" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="H295" s="21"/>
       <c r="J295" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="296" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="297" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="298" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="299" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="305" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="1:10" s="11" customFormat="1" collapsed="1" x14ac:dyDescent="0.25"/>
-    <row r="308" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="297" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="298" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="299" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="300" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="301" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="302" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="303" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="304" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="305" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="306" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="307" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H307" s="17"/>
+    </row>
+    <row r="308" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
         <v>257</v>
       </c>
+      <c r="H308" s="21"/>
       <c r="J308" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="309" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="310" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="311" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="312" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="313" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="314" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="315" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="316" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="317" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="318" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="319" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="320" spans="1:10" s="11" customFormat="1" collapsed="1" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="310" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="311" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="312" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="313" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="314" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="315" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="316" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="317" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="318" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="319" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="320" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H320" s="17"/>
+    </row>
+    <row r="321" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A321" s="10" t="s">
         <v>24</v>
       </c>
+      <c r="H321" s="21"/>
       <c r="J321" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="322" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>256</v>
       </c>
@@ -4978,26 +5080,29 @@
         <v>255</v>
       </c>
     </row>
-    <row r="323" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="329" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="330" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="331" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="332" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="333" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="334" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="324" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="325" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="326" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="327" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="328" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="329" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="330" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="331" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="332" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="333" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H333" s="17"/>
+    </row>
+    <row r="334" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="10" t="s">
         <v>254</v>
       </c>
+      <c r="H334" s="21"/>
       <c r="J334" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="335" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>253</v>
       </c>
@@ -5005,26 +5110,29 @@
         <v>250</v>
       </c>
     </row>
-    <row r="336" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="337" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="338" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="339" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="340" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="342" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="343" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="344" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="345" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="346" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="347" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="337" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="338" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="339" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="340" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="341" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="342" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="343" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="344" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="345" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="346" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H346" s="17"/>
+    </row>
+    <row r="347" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A347" s="10" t="s">
         <v>252</v>
       </c>
+      <c r="H347" s="21"/>
       <c r="J347" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="348" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>251</v>
       </c>
@@ -5032,26 +5140,29 @@
         <v>250</v>
       </c>
     </row>
-    <row r="349" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="350" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="351" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="352" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="353" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="354" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="355" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="356" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="357" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="358" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="359" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="360" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="350" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="351" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="352" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="353" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="354" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="355" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="356" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="357" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="358" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="359" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H359" s="17"/>
+    </row>
+    <row r="360" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A360" s="10" t="s">
         <v>249</v>
       </c>
+      <c r="H360" s="21"/>
       <c r="J360" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="361" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>247</v>
       </c>
@@ -5059,19 +5170,25 @@
         <v>246</v>
       </c>
     </row>
-    <row r="362" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="364" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="365" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="366" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="367" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="368" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="369" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="370" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="371" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="372" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="373" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="374" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="363" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="364" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="365" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="366" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="367" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="368" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="369" spans="8:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="370" spans="8:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="371" spans="8:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="372" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H372" s="22"/>
+    </row>
+    <row r="373" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H373" s="22"/>
+    </row>
+    <row r="374" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H374" s="22"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -5081,9 +5198,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D6B7E4-0C50-45F9-82CE-26F41FC338AF}">
   <dimension ref="A1:G309"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>374</v>
       </c>
@@ -5106,7 +5223,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:G11">Context_Input!A4:G13</f>
         <v>#Reactor</v>
@@ -5130,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <v>#Reactor</v>
       </c>
@@ -5153,7 +5270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <v>#Reactor</v>
       </c>
@@ -5176,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <v>#Reactor</v>
       </c>
@@ -5199,7 +5316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -5222,7 +5339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0</v>
       </c>
@@ -5245,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0</v>
       </c>
@@ -5268,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0</v>
       </c>
@@ -5291,7 +5408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0</v>
       </c>
@@ -5314,7 +5431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0</v>
       </c>
@@ -5337,7 +5454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="str" cm="1">
         <f t="array" ref="A12:G22">Context_Input!A16:G26</f>
         <v>#Vessel</v>
@@ -5361,7 +5478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <v>#Vessel</v>
       </c>
@@ -5384,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0</v>
       </c>
@@ -5407,7 +5524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0</v>
       </c>
@@ -5430,7 +5547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0</v>
       </c>
@@ -5453,7 +5570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0</v>
       </c>
@@ -5476,7 +5593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0</v>
       </c>
@@ -5499,7 +5616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0</v>
       </c>
@@ -5522,7 +5639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0</v>
       </c>
@@ -5545,7 +5662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0</v>
       </c>
@@ -5568,7 +5685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0</v>
       </c>
@@ -5591,7 +5708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="str" cm="1">
         <f t="array" ref="A23:G33">Context_Input!A29:G39</f>
         <v>#Stirrer</v>
@@ -5615,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <v>#Stirrer</v>
       </c>
@@ -5638,7 +5755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0</v>
       </c>
@@ -5661,7 +5778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0</v>
       </c>
@@ -5684,7 +5801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0</v>
       </c>
@@ -5707,7 +5824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0</v>
       </c>
@@ -5730,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0</v>
       </c>
@@ -5753,7 +5870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0</v>
       </c>
@@ -5776,7 +5893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0</v>
       </c>
@@ -5799,7 +5916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0</v>
       </c>
@@ -5822,7 +5939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0</v>
       </c>
@@ -5845,7 +5962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="str" cm="1">
         <f t="array" ref="A34:G44">Context_Input!A42:G52</f>
         <v>#Sparger</v>
@@ -5869,7 +5986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <v>#Sparger</v>
       </c>
@@ -5892,7 +6009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0</v>
       </c>
@@ -5915,7 +6032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0</v>
       </c>
@@ -5938,7 +6055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0</v>
       </c>
@@ -5961,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0</v>
       </c>
@@ -5984,7 +6101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0</v>
       </c>
@@ -6007,7 +6124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0</v>
       </c>
@@ -6030,7 +6147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0</v>
       </c>
@@ -6053,7 +6170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0</v>
       </c>
@@ -6076,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0</v>
       </c>
@@ -6099,7 +6216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="str" cm="1">
         <f t="array" ref="A45:G55">Context_Input!A55:G65</f>
         <v>#Jacket</v>
@@ -6123,7 +6240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <v>#Jacket</v>
       </c>
@@ -6146,7 +6263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0</v>
       </c>
@@ -6169,7 +6286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0</v>
       </c>
@@ -6192,7 +6309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0</v>
       </c>
@@ -6215,7 +6332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0</v>
       </c>
@@ -6238,7 +6355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0</v>
       </c>
@@ -6261,7 +6378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>0</v>
       </c>
@@ -6284,7 +6401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>0</v>
       </c>
@@ -6307,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>0</v>
       </c>
@@ -6330,7 +6447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>0</v>
       </c>
@@ -6353,7 +6470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="str" cm="1">
         <f t="array" ref="A56:G66">Context_Input!A68:G78</f>
         <v>#TemperatureSensor</v>
@@ -6377,7 +6494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <v>#TemperatureSensor</v>
       </c>
@@ -6400,7 +6517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>0</v>
       </c>
@@ -6423,7 +6540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>0</v>
       </c>
@@ -6446,7 +6563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>0</v>
       </c>
@@ -6469,7 +6586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>0</v>
       </c>
@@ -6492,7 +6609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>0</v>
       </c>
@@ -6515,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>0</v>
       </c>
@@ -6538,7 +6655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>0</v>
       </c>
@@ -6561,7 +6678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>0</v>
       </c>
@@ -6584,7 +6701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>0</v>
       </c>
@@ -6607,7 +6724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="str" cm="1">
         <f t="array" ref="A67:G77">Context_Input!A81:G91</f>
         <v>#PressureSensor</v>
@@ -6631,7 +6748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <v>#PressureSensor</v>
       </c>
@@ -6654,7 +6771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>0</v>
       </c>
@@ -6677,7 +6794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>0</v>
       </c>
@@ -6700,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>0</v>
       </c>
@@ -6723,7 +6840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>0</v>
       </c>
@@ -6746,7 +6863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>0</v>
       </c>
@@ -6769,7 +6886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>0</v>
       </c>
@@ -6792,7 +6909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>0</v>
       </c>
@@ -6815,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>0</v>
       </c>
@@ -6838,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>0</v>
       </c>
@@ -6861,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="str" cm="1">
         <f t="array" ref="A78:G88">Context_Input!A94:G104</f>
         <v>#MassFlowMeter</v>
@@ -6885,7 +7002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <v>#MassFlowMeter</v>
       </c>
@@ -6908,7 +7025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>0</v>
       </c>
@@ -6931,7 +7048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>0</v>
       </c>
@@ -6954,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>0</v>
       </c>
@@ -6977,7 +7094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>0</v>
       </c>
@@ -7000,7 +7117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>0</v>
       </c>
@@ -7023,7 +7140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>0</v>
       </c>
@@ -7046,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>0</v>
       </c>
@@ -7069,7 +7186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>0</v>
       </c>
@@ -7092,7 +7209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>0</v>
       </c>
@@ -7115,7 +7232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="str" cm="1">
         <f t="array" ref="A89:G100">Context_Input!A107:G118</f>
         <v>#Balance</v>
@@ -7139,7 +7256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <v>#Balance</v>
       </c>
@@ -7162,7 +7279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>0</v>
       </c>
@@ -7185,7 +7302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>0</v>
       </c>
@@ -7208,7 +7325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>0</v>
       </c>
@@ -7231,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>0</v>
       </c>
@@ -7254,7 +7371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>0</v>
       </c>
@@ -7277,7 +7394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>0</v>
       </c>
@@ -7300,7 +7417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>0</v>
       </c>
@@ -7323,7 +7440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>0</v>
       </c>
@@ -7346,7 +7463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>0</v>
       </c>
@@ -7369,7 +7486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>0</v>
       </c>
@@ -7392,7 +7509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="str" cm="1">
         <f t="array" ref="A101:G111">Context_Input!A124:G134</f>
         <v>#LiquidPhase</v>
@@ -7416,7 +7533,7 @@
         <v>#InitialMassFraction_Solvent_LiquidPhase</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
         <v>#LiquidPhase</v>
       </c>
@@ -7439,7 +7556,7 @@
         <v>#InitialMassFraction_Water_LiquidPhase</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
         <v>#LiquidPhase</v>
       </c>
@@ -7462,7 +7579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
         <v>#LiquidPhase</v>
       </c>
@@ -7485,7 +7602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>0</v>
       </c>
@@ -7508,7 +7625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>0</v>
       </c>
@@ -7531,7 +7648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>0</v>
       </c>
@@ -7554,7 +7671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>0</v>
       </c>
@@ -7577,7 +7694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>0</v>
       </c>
@@ -7600,7 +7717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>0</v>
       </c>
@@ -7623,7 +7740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>0</v>
       </c>
@@ -7646,7 +7763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="str" cm="1">
         <f t="array" ref="A112:G122">Context_Input!A137:G147</f>
         <v>#SolidPhase</v>
@@ -7670,7 +7787,7 @@
         <v>#RDY_Energy</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
         <v>#SolidPhase</v>
       </c>
@@ -7693,7 +7810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
         <v>#SolidPhase</v>
       </c>
@@ -7716,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>0</v>
       </c>
@@ -7739,7 +7856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>0</v>
       </c>
@@ -7762,7 +7879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>0</v>
       </c>
@@ -7785,7 +7902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>0</v>
       </c>
@@ -7808,7 +7925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>0</v>
       </c>
@@ -7831,7 +7948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>0</v>
       </c>
@@ -7854,7 +7971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>0</v>
       </c>
@@ -7877,7 +7994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>0</v>
       </c>
@@ -7900,7 +8017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="str" cm="1">
         <f t="array" ref="A123:G133">Context_Input!A150:G160</f>
         <v>#CatalystPhase</v>
@@ -7924,7 +8041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="str">
         <v>#CatalystPhase</v>
       </c>
@@ -7947,7 +8064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="str">
         <v>#CatalystPhase</v>
       </c>
@@ -7970,7 +8087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>0</v>
       </c>
@@ -7993,7 +8110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>0</v>
       </c>
@@ -8016,7 +8133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>0</v>
       </c>
@@ -8039,7 +8156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>0</v>
       </c>
@@ -8062,7 +8179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>0</v>
       </c>
@@ -8085,7 +8202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>0</v>
       </c>
@@ -8108,7 +8225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>0</v>
       </c>
@@ -8131,7 +8248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>0</v>
       </c>
@@ -8154,7 +8271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="str" cm="1">
         <f t="array" ref="A134:G144">Context_Input!A163:G173</f>
         <v>#GasPhase</v>
@@ -8178,7 +8295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="str">
         <v>#GasPhase</v>
       </c>
@@ -8201,7 +8318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="str">
         <v>#GasPhase</v>
       </c>
@@ -8224,7 +8341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>0</v>
       </c>
@@ -8247,7 +8364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>0</v>
       </c>
@@ -8270,7 +8387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>0</v>
       </c>
@@ -8293,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>0</v>
       </c>
@@ -8316,7 +8433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>0</v>
       </c>
@@ -8339,7 +8456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>0</v>
       </c>
@@ -8362,7 +8479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>0</v>
       </c>
@@ -8385,7 +8502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>0</v>
       </c>
@@ -8408,7 +8525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="str" cm="1">
         <f t="array" ref="A145:G155">Context_Input!A176:G186</f>
         <v>#DispersedGasPhase</v>
@@ -8432,7 +8549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="str">
         <v>#DispersedGasPhase</v>
       </c>
@@ -8455,7 +8572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="str">
         <v>#DispersedGasPhase</v>
       </c>
@@ -8478,7 +8595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>0</v>
       </c>
@@ -8501,7 +8618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>0</v>
       </c>
@@ -8524,7 +8641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>0</v>
       </c>
@@ -8547,7 +8664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>0</v>
       </c>
@@ -8570,7 +8687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>0</v>
       </c>
@@ -8593,7 +8710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>0</v>
       </c>
@@ -8616,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>0</v>
       </c>
@@ -8639,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>0</v>
       </c>
@@ -8662,7 +8779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="str" cm="1">
         <f t="array" ref="A156:G166">Context_Input!A189:G199</f>
         <v>#CoolingFluidPhase</v>
@@ -8686,7 +8803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="str">
         <v>#CoolingFluidPhase</v>
       </c>
@@ -8709,7 +8826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="str">
         <v>#CoolingFluidPhase</v>
       </c>
@@ -8732,7 +8849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>0</v>
       </c>
@@ -8755,7 +8872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>0</v>
       </c>
@@ -8778,7 +8895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>0</v>
       </c>
@@ -8801,7 +8918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>0</v>
       </c>
@@ -8824,7 +8941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>0</v>
       </c>
@@ -8847,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>0</v>
       </c>
@@ -8870,7 +8987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>0</v>
       </c>
@@ -8893,7 +9010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>0</v>
       </c>
@@ -8916,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="str" cm="1">
         <f t="array" ref="A167:G177">Context_Input!A202:G212</f>
         <v>#HydrogenSpargerPhase</v>
@@ -8940,7 +9057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="str">
         <v>#HydrogenSpargerPhase</v>
       </c>
@@ -8963,7 +9080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="str">
         <v>#HydrogenSpargerPhase</v>
       </c>
@@ -8986,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>0</v>
       </c>
@@ -9009,7 +9126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>0</v>
       </c>
@@ -9032,7 +9149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>0</v>
       </c>
@@ -9055,7 +9172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>0</v>
       </c>
@@ -9078,7 +9195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>0</v>
       </c>
@@ -9101,7 +9218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>0</v>
       </c>
@@ -9124,7 +9241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>0</v>
       </c>
@@ -9147,7 +9264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>0</v>
       </c>
@@ -9170,7 +9287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="str" cm="1">
         <f t="array" ref="A178:G188">Context_Input!A215:G225</f>
         <v>#CleaningFluidPhase</v>
@@ -9194,7 +9311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>0</v>
       </c>
@@ -9217,7 +9334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>0</v>
       </c>
@@ -9240,7 +9357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>0</v>
       </c>
@@ -9263,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>0</v>
       </c>
@@ -9286,7 +9403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>0</v>
       </c>
@@ -9309,7 +9426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>0</v>
       </c>
@@ -9332,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>0</v>
       </c>
@@ -9355,7 +9472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>0</v>
       </c>
@@ -9378,7 +9495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>0</v>
       </c>
@@ -9401,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>0</v>
       </c>
@@ -9424,7 +9541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="str" cm="1">
         <f t="array" ref="A189:G199">Context_Input!A231:G241</f>
         <v>#H2</v>
@@ -9448,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="str">
         <v>#H3</v>
       </c>
@@ -9471,7 +9588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="str">
         <v>#H4</v>
       </c>
@@ -9494,7 +9611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>0</v>
       </c>
@@ -9517,7 +9634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>0</v>
       </c>
@@ -9540,7 +9657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>0</v>
       </c>
@@ -9563,7 +9680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>0</v>
       </c>
@@ -9586,7 +9703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>0</v>
       </c>
@@ -9609,7 +9726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>0</v>
       </c>
@@ -9632,7 +9749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>0</v>
       </c>
@@ -9655,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>0</v>
       </c>
@@ -9678,7 +9795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="str" cm="1">
         <f t="array" ref="A200:G210">Context_Input!A244:G254</f>
         <v>#H2O</v>
@@ -9702,7 +9819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>0</v>
       </c>
@@ -9725,7 +9842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>0</v>
       </c>
@@ -9748,7 +9865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>0</v>
       </c>
@@ -9771,7 +9888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>0</v>
       </c>
@@ -9794,7 +9911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>0</v>
       </c>
@@ -9817,7 +9934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>0</v>
       </c>
@@ -9840,7 +9957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>0</v>
       </c>
@@ -9863,7 +9980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>0</v>
       </c>
@@ -9886,7 +10003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>0</v>
       </c>
@@ -9909,7 +10026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>0</v>
       </c>
@@ -9932,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="str" cm="1">
         <f t="array" ref="A211:G221">Context_Input!A257:G267</f>
         <v>#Solvent</v>
@@ -9956,7 +10073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>0</v>
       </c>
@@ -9979,7 +10096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>0</v>
       </c>
@@ -10002,7 +10119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>0</v>
       </c>
@@ -10025,7 +10142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>0</v>
       </c>
@@ -10048,7 +10165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>0</v>
       </c>
@@ -10071,7 +10188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>0</v>
       </c>
@@ -10094,7 +10211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>0</v>
       </c>
@@ -10117,7 +10234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>0</v>
       </c>
@@ -10140,7 +10257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>0</v>
       </c>
@@ -10163,7 +10280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>0</v>
       </c>
@@ -10186,7 +10303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="str" cm="1">
         <f t="array" ref="A222:G232">Context_Input!A270:G280</f>
         <v>#RDY</v>
@@ -10210,7 +10327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="str">
         <v>#RDY</v>
       </c>
@@ -10233,7 +10350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="str">
         <v>#RDY</v>
       </c>
@@ -10256,7 +10373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>0</v>
       </c>
@@ -10279,7 +10396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>0</v>
       </c>
@@ -10302,7 +10419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>0</v>
       </c>
@@ -10325,7 +10442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>0</v>
       </c>
@@ -10348,7 +10465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>0</v>
       </c>
@@ -10371,7 +10488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>0</v>
       </c>
@@ -10394,7 +10511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>0</v>
       </c>
@@ -10417,7 +10534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>0</v>
       </c>
@@ -10440,7 +10557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" cm="1">
         <f t="array" ref="A233:G243">Context_Input!A283:G293</f>
         <v>0</v>
@@ -10464,7 +10581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>0</v>
       </c>
@@ -10487,7 +10604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>0</v>
       </c>
@@ -10510,7 +10627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>0</v>
       </c>
@@ -10533,7 +10650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>0</v>
       </c>
@@ -10556,7 +10673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>0</v>
       </c>
@@ -10579,7 +10696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>0</v>
       </c>
@@ -10602,7 +10719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>0</v>
       </c>
@@ -10625,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>0</v>
       </c>
@@ -10648,7 +10765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>0</v>
       </c>
@@ -10671,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>0</v>
       </c>
@@ -10694,7 +10811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" cm="1">
         <f t="array" ref="A244:G254">Context_Input!A296:G306</f>
         <v>0</v>
@@ -10718,7 +10835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>0</v>
       </c>
@@ -10741,7 +10858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>0</v>
       </c>
@@ -10764,7 +10881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>0</v>
       </c>
@@ -10787,7 +10904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>0</v>
       </c>
@@ -10810,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>0</v>
       </c>
@@ -10833,7 +10950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>0</v>
       </c>
@@ -10856,7 +10973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>0</v>
       </c>
@@ -10879,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>0</v>
       </c>
@@ -10902,7 +11019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>0</v>
       </c>
@@ -10925,7 +11042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>0</v>
       </c>
@@ -10948,7 +11065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" cm="1">
         <f t="array" ref="A255:G265">Context_Input!A309:G319</f>
         <v>0</v>
@@ -10972,7 +11089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>0</v>
       </c>
@@ -10995,7 +11112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>0</v>
       </c>
@@ -11018,7 +11135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>0</v>
       </c>
@@ -11041,7 +11158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>0</v>
       </c>
@@ -11064,7 +11181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>0</v>
       </c>
@@ -11087,7 +11204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>0</v>
       </c>
@@ -11110,7 +11227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>0</v>
       </c>
@@ -11133,7 +11250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>0</v>
       </c>
@@ -11156,7 +11273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>0</v>
       </c>
@@ -11179,7 +11296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>0</v>
       </c>
@@ -11202,7 +11319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="str" cm="1">
         <f t="array" ref="A266:G276">Context_Input!A322:G332</f>
         <v>#RDEt</v>
@@ -11226,7 +11343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>0</v>
       </c>
@@ -11249,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>0</v>
       </c>
@@ -11272,7 +11389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>0</v>
       </c>
@@ -11295,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>0</v>
       </c>
@@ -11318,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>0</v>
       </c>
@@ -11341,7 +11458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>0</v>
       </c>
@@ -11364,7 +11481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>0</v>
       </c>
@@ -11387,7 +11504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>0</v>
       </c>
@@ -11410,7 +11527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>0</v>
       </c>
@@ -11433,7 +11550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>0</v>
       </c>
@@ -11456,7 +11573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="str" cm="1">
         <f t="array" ref="A277:G287">Context_Input!A335:G345</f>
         <v>#Dimer1</v>
@@ -11480,7 +11597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>0</v>
       </c>
@@ -11503,7 +11620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>0</v>
       </c>
@@ -11526,7 +11643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>0</v>
       </c>
@@ -11549,7 +11666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>0</v>
       </c>
@@ -11572,7 +11689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>0</v>
       </c>
@@ -11595,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>0</v>
       </c>
@@ -11618,7 +11735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>0</v>
       </c>
@@ -11641,7 +11758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>0</v>
       </c>
@@ -11664,7 +11781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>0</v>
       </c>
@@ -11687,7 +11804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>0</v>
       </c>
@@ -11710,7 +11827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="str" cm="1">
         <f t="array" ref="A288:G298">Context_Input!A348:G358</f>
         <v>#Dimer2</v>
@@ -11734,7 +11851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>0</v>
       </c>
@@ -11757,7 +11874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>0</v>
       </c>
@@ -11780,7 +11897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>0</v>
       </c>
@@ -11803,7 +11920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>0</v>
       </c>
@@ -11826,7 +11943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>0</v>
       </c>
@@ -11849,7 +11966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>0</v>
       </c>
@@ -11872,7 +11989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>0</v>
       </c>
@@ -11895,7 +12012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>0</v>
       </c>
@@ -11918,7 +12035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>0</v>
       </c>
@@ -11941,7 +12058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>0</v>
       </c>
@@ -11964,7 +12081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" t="str" cm="1">
         <f t="array" ref="A299:G309">Context_Input!A361:G371</f>
         <v>#Pt</v>
@@ -11988,7 +12105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>0</v>
       </c>
@@ -12011,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>0</v>
       </c>
@@ -12034,7 +12151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>0</v>
       </c>
@@ -12057,7 +12174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>0</v>
       </c>
@@ -12080,7 +12197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>0</v>
       </c>
@@ -12103,7 +12220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>0</v>
       </c>
@@ -12126,7 +12243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>0</v>
       </c>
@@ -12149,7 +12266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>0</v>
       </c>
@@ -12172,7 +12289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>0</v>
       </c>
@@ -12195,7 +12312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>0</v>
       </c>
@@ -12226,17 +12343,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A707C2C-4F81-45CE-8355-AEA9654420E5}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
-    <col min="11" max="11" width="24.140625" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
+    <col min="11" max="11" width="24.109375" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>374</v>
       </c>
@@ -12253,7 +12370,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>477</v>
       </c>
@@ -12264,7 +12381,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>474</v>
       </c>
@@ -12277,13 +12394,13 @@
       <c r="K4" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="15" t="s">
         <v>472</v>
       </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="s">
         <v>471</v>
@@ -12301,7 +12418,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>407</v>
       </c>
@@ -12324,7 +12441,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>459</v>
       </c>
@@ -12347,7 +12464,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>459</v>
       </c>
@@ -12373,7 +12490,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -12390,7 +12507,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>452</v>
       </c>
@@ -12407,7 +12524,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -12421,7 +12538,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>261</v>
       </c>
@@ -12432,7 +12549,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>266</v>
       </c>
@@ -12443,7 +12560,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>297</v>
       </c>
@@ -12466,7 +12583,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>320</v>
       </c>
@@ -12486,7 +12603,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>327</v>
       </c>
@@ -12497,7 +12614,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>282</v>
       </c>
@@ -12514,7 +12631,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>362</v>
       </c>
@@ -12534,7 +12651,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>338</v>
       </c>
@@ -12551,7 +12668,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>346</v>
       </c>
@@ -12568,7 +12685,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>359</v>
       </c>
@@ -12585,7 +12702,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>419</v>
       </c>
@@ -12605,7 +12722,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>415</v>
       </c>
@@ -12613,7 +12730,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>311</v>
       </c>
@@ -12624,7 +12741,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>411</v>
       </c>
@@ -12635,7 +12752,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>403</v>
       </c>
@@ -12646,7 +12763,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>407</v>
       </c>
@@ -12657,7 +12774,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>404</v>
       </c>
@@ -12668,7 +12785,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>401</v>
       </c>
@@ -12676,7 +12793,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>399</v>
       </c>
@@ -12684,7 +12801,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>397</v>
       </c>
@@ -12692,12 +12809,12 @@
         <v>383</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E32" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>396</v>
       </c>
@@ -12708,7 +12825,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>394</v>
       </c>
@@ -12719,7 +12836,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>391</v>
       </c>
@@ -12727,7 +12844,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>389</v>
       </c>
@@ -12735,7 +12852,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>387</v>
       </c>
@@ -12746,7 +12863,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>336</v>
       </c>
@@ -12754,7 +12871,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>370</v>
       </c>
@@ -12762,7 +12879,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>342</v>
       </c>
@@ -12770,7 +12887,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>350</v>
       </c>
@@ -12778,7 +12895,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>355</v>
       </c>
@@ -12786,7 +12903,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>335</v>
       </c>
@@ -12794,7 +12911,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>368</v>
       </c>
@@ -12802,7 +12919,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>341</v>
       </c>
@@ -12810,7 +12927,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>349</v>
       </c>
@@ -12818,7 +12935,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>354</v>
       </c>

--- a/CASESTUDY_Hydrogenation.xlsx
+++ b/CASESTUDY_Hydrogenation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/lf576_cam_ac_uk/Documents/04_Coding/hydrogenation/current_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F8180BA-4D06-4597-B6A5-06D2096C39F6}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B5A8AA5-601C-4729-92E8-464BFE446E83}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="490">
   <si>
     <t>This is the file containing all the information about the Hydrogenation Process Case Study</t>
   </si>
@@ -1512,12 +1512,6 @@
   </si>
   <si>
     <t>describes Context</t>
-  </si>
-  <si>
-    <t>#H3</t>
-  </si>
-  <si>
-    <t>#H4</t>
   </si>
   <si>
     <t>In Context_Input können die Devices, Phases und Molecules eingefügt werden, und dann kann man direkt deren Kontext beschreiben</t>
@@ -2034,27 +2028,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -4335,7 +4329,7 @@
         <v>313</v>
       </c>
       <c r="I94" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="95" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -4721,7 +4715,7 @@
         <v>283</v>
       </c>
       <c r="I189" s="14" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="190" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -4853,7 +4847,7 @@
     </row>
     <row r="232" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>482</v>
+        <v>115</v>
       </c>
       <c r="C232" t="s">
         <v>269</v>
@@ -4861,7 +4855,7 @@
     </row>
     <row r="233" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>483</v>
+        <v>115</v>
       </c>
       <c r="C233" t="s">
         <v>268</v>
@@ -4898,7 +4892,7 @@
         <v>262</v>
       </c>
       <c r="I244" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="245" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
@@ -9567,7 +9561,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="str">
-        <v>#H3</v>
+        <v>#H2</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -9590,7 +9584,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="str">
-        <v>#H4</v>
+        <v>#H2</v>
       </c>
       <c r="B191">
         <v>0</v>

--- a/CASESTUDY_Hydrogenation.xlsx
+++ b/CASESTUDY_Hydrogenation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/lf576_cam_ac_uk/Documents/04_Coding/hydrogenation/current_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B5A8AA5-601C-4729-92E8-464BFE446E83}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C125219F-38CE-4786-915C-CFB519907254}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="493">
   <si>
     <t>This is the file containing all the information about the Hydrogenation Process Case Study</t>
   </si>
@@ -1536,6 +1536,15 @@
   </si>
   <si>
     <t>Reactor Energy würde ich prinzipiell nicht wirklich hiermit verbinden, aber da ich definiert habe dass MassFlowMeter ein Teil von Reactor ist muss ich das der Vollständigkeit halber auch hier aufführen</t>
+  </si>
+  <si>
+    <t>#Reaction1</t>
+  </si>
+  <si>
+    <t>#Reaction2</t>
+  </si>
+  <si>
+    <t>#Reaction3</t>
   </si>
 </sst>
 </file>
@@ -1673,10 +1682,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1699,6 +1708,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2019,34 +2032,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D6EF24-A5F2-4E49-9641-E94D8B75807A}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>486</v>
       </c>
@@ -2060,22 +2073,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A819942F-56E1-4F4B-AB2B-0557B5EACCFB}">
   <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1:E64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="52.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" customWidth="1"/>
-    <col min="8" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.109375" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -2092,7 +2105,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -2109,7 +2122,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -2123,7 +2136,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>10</v>
       </c>
@@ -2137,7 +2150,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -2151,7 +2164,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>78</v>
       </c>
@@ -2159,32 +2172,32 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>77</v>
       </c>
@@ -2192,33 +2205,33 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>76</v>
       </c>
@@ -2232,7 +2245,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>72</v>
       </c>
@@ -2243,7 +2256,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>69</v>
       </c>
@@ -2254,7 +2267,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>66</v>
       </c>
@@ -2265,7 +2278,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>63</v>
       </c>
@@ -2273,7 +2286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>61</v>
       </c>
@@ -2281,32 +2294,32 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>55</v>
       </c>
@@ -2323,7 +2336,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -2334,7 +2347,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -2345,7 +2358,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -2356,7 +2369,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2367,7 +2380,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2378,7 +2391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2389,7 +2402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>36</v>
       </c>
@@ -2400,7 +2413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2411,7 +2424,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
@@ -2422,7 +2435,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>30</v>
       </c>
@@ -2433,7 +2446,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>28</v>
       </c>
@@ -2444,7 +2457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>26</v>
       </c>
@@ -2455,7 +2468,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>24</v>
       </c>
@@ -2466,7 +2479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -2477,7 +2490,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>18</v>
       </c>
@@ -2488,7 +2501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -2496,14 +2509,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -2514,17 +2527,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>8</v>
       </c>
@@ -2535,7 +2548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -2543,7 +2556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -2563,22 +2576,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF69EE7-86F4-48C0-B75B-749BFC7A4C35}">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1:N87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
-    <col min="3" max="3" width="26.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="22.109375" customWidth="1"/>
-    <col min="6" max="6" width="28.88671875" customWidth="1"/>
-    <col min="7" max="7" width="23.5546875" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="22.6640625" customWidth="1"/>
-    <col min="11" max="11" width="33.88671875" customWidth="1"/>
-    <col min="12" max="12" width="30.5546875" customWidth="1"/>
-    <col min="13" max="13" width="22.44140625" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="11" max="11" width="33.85546875" customWidth="1"/>
+    <col min="12" max="12" width="30.5703125" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -2622,8 +2635,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
@@ -2664,7 +2677,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="C4" t="s">
         <v>185</v>
@@ -2691,7 +2704,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
       <c r="C5" t="s">
         <v>222</v>
@@ -2706,7 +2719,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
       <c r="C6" t="s">
         <v>137</v>
@@ -2721,7 +2734,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
       <c r="C7" t="s">
         <v>123</v>
@@ -2736,7 +2749,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="7" t="s">
         <v>219</v>
@@ -2751,7 +2764,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="7" t="s">
         <v>189</v>
@@ -2760,19 +2773,19 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
     </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>216</v>
       </c>
@@ -2813,7 +2826,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="E15" t="s">
         <v>208</v>
@@ -2840,7 +2853,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" t="s">
         <v>123</v>
@@ -2867,7 +2880,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" t="s">
         <v>189</v>
@@ -2882,22 +2895,22 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>199</v>
       </c>
@@ -2938,7 +2951,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" t="s">
         <v>137</v>
@@ -2965,7 +2978,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
       <c r="C25" t="s">
         <v>123</v>
@@ -2986,7 +2999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="4"/>
       <c r="C26" t="s">
         <v>189</v>
@@ -3007,16 +3020,16 @@
         <v>167</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
         <v>186</v>
       </c>
@@ -3057,7 +3070,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="4"/>
       <c r="C31" t="s">
         <v>137</v>
@@ -3078,7 +3091,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
       <c r="C32" t="s">
         <v>123</v>
@@ -3099,7 +3112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="4"/>
       <c r="E33" t="s">
         <v>170</v>
@@ -3114,16 +3127,16 @@
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
     </row>
-    <row r="36" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
         <v>5</v>
       </c>
@@ -3158,7 +3171,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" s="4"/>
       <c r="C38" t="s">
         <v>114</v>
@@ -3191,7 +3204,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" t="s">
         <v>109</v>
@@ -3224,7 +3237,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="7" t="s">
         <v>103</v>
@@ -3246,7 +3259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="7" t="s">
         <v>101</v>
@@ -3262,7 +3275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" s="4"/>
       <c r="C42" s="6" t="s">
         <v>123</v>
@@ -3278,7 +3291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" s="4"/>
       <c r="E43" s="5"/>
       <c r="M43" t="s">
@@ -3288,7 +3301,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" s="4"/>
       <c r="E44" s="5"/>
       <c r="M44" t="s">
@@ -3298,17 +3311,17 @@
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" s="4"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="4"/>
     </row>
-    <row r="47" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
         <v>150</v>
       </c>
@@ -3343,7 +3356,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="4"/>
       <c r="C49" t="s">
         <v>114</v>
@@ -3370,7 +3383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B50" s="4"/>
       <c r="C50" t="s">
         <v>109</v>
@@ -3397,21 +3410,21 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="4"/>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
       <c r="C52" t="s">
         <v>101</v>
       </c>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" s="4"/>
       <c r="C53" s="6" t="s">
         <v>123</v>
@@ -3421,13 +3434,13 @@
       </c>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B54" s="4"/>
     </row>
-    <row r="55" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
         <v>143</v>
       </c>
@@ -3462,7 +3475,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B57" s="4"/>
       <c r="C57" t="s">
         <v>114</v>
@@ -3495,7 +3508,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
       <c r="C58" t="s">
         <v>109</v>
@@ -3522,7 +3535,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
         <v>103</v>
@@ -3541,14 +3554,14 @@
         <v>124</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B60" s="4"/>
       <c r="C60" s="7" t="s">
         <v>101</v>
       </c>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" s="4"/>
       <c r="C61" s="6" t="s">
         <v>123</v>
@@ -3558,17 +3571,17 @@
       </c>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B62" s="4"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B63" s="4"/>
     </row>
-    <row r="64" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
         <v>121</v>
       </c>
@@ -3597,7 +3610,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B66" s="4"/>
       <c r="C66" t="s">
         <v>114</v>
@@ -3624,7 +3637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B67" s="4"/>
       <c r="C67" t="s">
         <v>109</v>
@@ -3645,7 +3658,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B68" s="4"/>
       <c r="C68" t="s">
         <v>103</v>
@@ -3655,65 +3668,65 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="4"/>
       <c r="C69" t="s">
         <v>101</v>
       </c>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B70" s="4"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" s="4"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B72" s="4"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B73" s="4"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B74" s="4"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B75" s="4"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B76" s="4"/>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B77" s="4"/>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="4"/>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B79" s="4"/>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B80" s="4"/>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B81" s="4"/>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B82" s="4"/>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B83" s="4"/>
     </row>
-    <row r="84" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>18</v>
       </c>
@@ -3742,12 +3755,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
         <v>92</v>
       </c>
@@ -3759,19 +3772,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D5FB7C-FC33-457D-B6B0-7F2ECBB63948}">
-  <dimension ref="A1:J374"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K374"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="51.5703125" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="16" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>374</v>
       </c>
@@ -3803,10 +3816,10 @@
         <v>371</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H2" s="17"/>
     </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>86</v>
       </c>
@@ -3815,7 +3828,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>360</v>
       </c>
@@ -3832,7 +3845,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="5" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>360</v>
       </c>
@@ -3849,7 +3862,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>360</v>
       </c>
@@ -3866,7 +3879,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>360</v>
       </c>
@@ -3877,24 +3890,24 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H8" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H9" s="16" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>357</v>
       </c>
@@ -3903,7 +3916,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>356</v>
       </c>
@@ -3920,7 +3933,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>356</v>
       </c>
@@ -3934,31 +3947,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H18" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="19" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H19" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H20" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H27" s="17"/>
     </row>
-    <row r="28" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
@@ -3969,7 +3982,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>351</v>
       </c>
@@ -3986,7 +3999,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>351</v>
       </c>
@@ -4003,39 +4016,39 @@
         <v>303</v>
       </c>
     </row>
-    <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H31" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="32" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H32" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="33" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H33" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H34" s="16" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="35" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H35" s="16" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="36" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H40" s="17"/>
     </row>
-    <row r="41" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
@@ -4044,7 +4057,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>343</v>
       </c>
@@ -4061,7 +4074,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="43" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>343</v>
       </c>
@@ -4078,31 +4091,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="44" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H44" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H45" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H46" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="50" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="53" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H53" s="17"/>
     </row>
-    <row r="54" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
@@ -4111,7 +4124,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>337</v>
       </c>
@@ -4128,7 +4141,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>337</v>
       </c>
@@ -4145,31 +4158,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H57" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="58" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H58" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="59" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H59" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H66" s="17"/>
     </row>
-    <row r="67" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>332</v>
       </c>
@@ -4178,7 +4191,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>331</v>
       </c>
@@ -4195,7 +4208,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="69" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>331</v>
       </c>
@@ -4212,31 +4225,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="70" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H70" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H71" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H72" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H79" s="17"/>
     </row>
-    <row r="80" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>325</v>
       </c>
@@ -4245,7 +4258,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>324</v>
       </c>
@@ -4262,7 +4275,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="82" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>324</v>
       </c>
@@ -4279,31 +4292,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="83" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H83" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="84" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H84" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="85" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H85" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="86" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="88" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H92" s="17"/>
     </row>
-    <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>318</v>
       </c>
@@ -4312,7 +4325,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>317</v>
       </c>
@@ -4332,7 +4345,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="95" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>317</v>
       </c>
@@ -4349,31 +4362,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="96" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H96" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="97" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H97" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="98" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H98" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="101" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="102" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="103" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="104" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="105" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H105" s="17"/>
     </row>
-    <row r="106" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>309</v>
       </c>
@@ -4382,13 +4395,16 @@
         <v>90</v>
       </c>
     </row>
-    <row r="107" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>308</v>
       </c>
       <c r="B107" t="s">
         <v>307</v>
       </c>
+      <c r="C107" t="s">
+        <v>419</v>
+      </c>
       <c r="D107" t="s">
         <v>306</v>
       </c>
@@ -4396,52 +4412,61 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>308</v>
       </c>
       <c r="B108" t="s">
         <v>304</v>
       </c>
+      <c r="C108" t="s">
+        <v>258</v>
+      </c>
       <c r="H108" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="109" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>452</v>
+      </c>
       <c r="H109" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="110" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C110" t="s">
+        <v>250</v>
+      </c>
       <c r="H110" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="111" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H111" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="112" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="113" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="115" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="116" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="117" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H119" s="19"/>
     </row>
-    <row r="120" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H120" s="19"/>
     </row>
-    <row r="121" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H121" s="19"/>
     </row>
-    <row r="122" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H122" s="19"/>
     </row>
-    <row r="123" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>85</v>
       </c>
@@ -4450,7 +4475,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>299</v>
       </c>
@@ -4467,7 +4492,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="125" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>299</v>
       </c>
@@ -4478,33 +4503,43 @@
         <v>266</v>
       </c>
     </row>
-    <row r="126" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>299</v>
       </c>
       <c r="E126" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="G126" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>299</v>
       </c>
       <c r="E127" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="129" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="130" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="131" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="132" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="133" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="134" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="135" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G127" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="G128" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H135" s="17"/>
     </row>
-    <row r="136" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="13" t="s">
         <v>80</v>
       </c>
@@ -4513,7 +4548,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="137" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>296</v>
       </c>
@@ -4527,15 +4562,18 @@
         <v>295</v>
       </c>
     </row>
-    <row r="138" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>296</v>
       </c>
       <c r="E138" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="G138" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>296</v>
       </c>
@@ -4543,18 +4581,18 @@
         <v>287</v>
       </c>
     </row>
-    <row r="140" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="141" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="142" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="143" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="144" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="145" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="146" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="147" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="148" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H148" s="17"/>
     </row>
-    <row r="149" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="13" t="s">
         <v>78</v>
       </c>
@@ -4563,7 +4601,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>294</v>
       </c>
@@ -4573,35 +4611,44 @@
       <c r="E150" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="G150" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>294</v>
       </c>
       <c r="E151" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="G151" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>294</v>
       </c>
       <c r="E152" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="154" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="155" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="156" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="157" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="158" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="159" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="160" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="161" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G152" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H161" s="17"/>
     </row>
-    <row r="162" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="13" t="s">
         <v>83</v>
       </c>
@@ -4610,7 +4657,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="163" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>293</v>
       </c>
@@ -4621,7 +4668,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="164" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>293</v>
       </c>
@@ -4629,7 +4676,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="165" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>293</v>
       </c>
@@ -4637,18 +4684,18 @@
         <v>287</v>
       </c>
     </row>
-    <row r="166" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="167" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="168" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="169" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="170" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="171" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="172" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="173" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="174" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H174" s="17"/>
     </row>
-    <row r="175" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="13" t="s">
         <v>292</v>
       </c>
@@ -4657,7 +4704,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="176" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>291</v>
       </c>
@@ -4667,8 +4714,11 @@
       <c r="E176" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="G176" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>291</v>
       </c>
@@ -4676,7 +4726,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="178" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>291</v>
       </c>
@@ -4684,18 +4734,18 @@
         <v>287</v>
       </c>
     </row>
-    <row r="179" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="180" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="181" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="182" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="183" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="184" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="185" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="186" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="187" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H187" s="17"/>
     </row>
-    <row r="188" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="13" t="s">
         <v>286</v>
       </c>
@@ -4704,7 +4754,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="189" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>285</v>
       </c>
@@ -4714,11 +4764,11 @@
       <c r="E189" t="s">
         <v>283</v>
       </c>
-      <c r="I189" s="14" t="s">
+      <c r="I189" s="15" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="190" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>285</v>
       </c>
@@ -4726,7 +4776,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="191" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>285</v>
       </c>
@@ -4734,18 +4784,18 @@
         <v>280</v>
       </c>
     </row>
-    <row r="192" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="193" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="194" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="195" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="196" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="197" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="198" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="199" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="200" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H200" s="17"/>
     </row>
-    <row r="201" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="13" t="s">
         <v>279</v>
       </c>
@@ -4754,7 +4804,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="202" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>278</v>
       </c>
@@ -4765,7 +4815,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="203" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>278</v>
       </c>
@@ -4773,7 +4823,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="204" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>278</v>
       </c>
@@ -4781,18 +4831,18 @@
         <v>274</v>
       </c>
     </row>
-    <row r="205" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="206" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="207" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="208" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="209" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="210" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="211" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="212" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="213" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H213" s="17"/>
     </row>
-    <row r="214" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="13" t="s">
         <v>273</v>
       </c>
@@ -4801,34 +4851,34 @@
         <v>89</v>
       </c>
     </row>
-    <row r="215" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="216" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="217" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="218" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="219" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="220" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="221" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="222" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="223" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="224" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="225" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="226" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H226" s="19"/>
     </row>
-    <row r="227" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H227" s="19"/>
     </row>
-    <row r="228" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H228" s="19"/>
     </row>
-    <row r="229" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H229" s="19"/>
     </row>
-    <row r="230" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
         <v>271</v>
       </c>
@@ -4837,7 +4887,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="231" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>115</v>
       </c>
@@ -4845,7 +4895,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="232" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>115</v>
       </c>
@@ -4853,7 +4903,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="233" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>115</v>
       </c>
@@ -4861,18 +4911,18 @@
         <v>268</v>
       </c>
     </row>
-    <row r="234" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="235" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="236" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="237" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="238" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="239" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="240" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="241" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="242" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H242" s="17"/>
     </row>
-    <row r="243" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
         <v>18</v>
       </c>
@@ -4881,7 +4931,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="244" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>267</v>
       </c>
@@ -4891,24 +4941,24 @@
       <c r="E244" t="s">
         <v>262</v>
       </c>
-      <c r="I244" s="14" t="s">
+      <c r="I244" s="15" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="245" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="246" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="247" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="248" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="249" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="250" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="251" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="252" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="253" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="254" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H255" s="17"/>
     </row>
-    <row r="256" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
         <v>265</v>
       </c>
@@ -4917,7 +4967,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="257" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>264</v>
       </c>
@@ -4927,24 +4977,24 @@
       <c r="E257" t="s">
         <v>262</v>
       </c>
-      <c r="I257" s="14" t="s">
+      <c r="I257" s="15" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="258" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="259" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="260" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="261" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="262" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="263" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="264" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="265" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="266" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="267" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="268" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H268" s="17"/>
     </row>
-    <row r="269" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
         <v>40</v>
       </c>
@@ -4953,7 +5003,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="270" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>146</v>
       </c>
@@ -4961,7 +5011,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="271" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>146</v>
       </c>
@@ -4969,7 +5019,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="272" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>146</v>
       </c>
@@ -4977,18 +5027,18 @@
         <v>258</v>
       </c>
     </row>
-    <row r="273" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="274" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="275" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="276" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="277" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="278" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="279" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="280" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="281" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H281" s="17"/>
     </row>
-    <row r="282" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
         <v>36</v>
       </c>
@@ -4997,21 +5047,21 @@
         <v>248</v>
       </c>
     </row>
-    <row r="283" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="284" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="285" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="286" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="287" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="288" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="289" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="290" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="291" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="292" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="293" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="294" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H294" s="17"/>
     </row>
-    <row r="295" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
         <v>32</v>
       </c>
@@ -5020,21 +5070,21 @@
         <v>248</v>
       </c>
     </row>
-    <row r="296" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="297" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="298" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="299" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="300" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="301" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="302" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="303" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="304" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="305" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="306" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="307" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H307" s="17"/>
     </row>
-    <row r="308" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
         <v>257</v>
       </c>
@@ -5043,21 +5093,21 @@
         <v>248</v>
       </c>
     </row>
-    <row r="309" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="310" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="311" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="312" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="313" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="314" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="315" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="316" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="317" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="318" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="319" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="320" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H320" s="17"/>
     </row>
-    <row r="321" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
         <v>24</v>
       </c>
@@ -5066,7 +5116,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="322" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>256</v>
       </c>
@@ -5074,20 +5124,20 @@
         <v>255</v>
       </c>
     </row>
-    <row r="323" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="324" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="325" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="326" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="327" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="328" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="329" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="330" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="331" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="332" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="333" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H333" s="17"/>
     </row>
-    <row r="334" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
         <v>254</v>
       </c>
@@ -5096,7 +5146,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="335" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>253</v>
       </c>
@@ -5104,20 +5154,20 @@
         <v>250</v>
       </c>
     </row>
-    <row r="336" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="337" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="338" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="339" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="340" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="341" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="342" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="343" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="344" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="345" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="346" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H346" s="17"/>
     </row>
-    <row r="347" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
         <v>252</v>
       </c>
@@ -5126,7 +5176,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="348" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>251</v>
       </c>
@@ -5134,20 +5184,20 @@
         <v>250</v>
       </c>
     </row>
-    <row r="349" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="350" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="351" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="352" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="353" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="354" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="355" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="356" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="357" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="358" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="359" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H359" s="17"/>
     </row>
-    <row r="360" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
         <v>249</v>
       </c>
@@ -5156,7 +5206,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="361" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>247</v>
       </c>
@@ -5164,23 +5214,23 @@
         <v>246</v>
       </c>
     </row>
-    <row r="362" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="363" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="364" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="365" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="366" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="367" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="368" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="369" spans="8:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="370" spans="8:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="371" spans="8:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="372" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="8:8" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="8:8" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="8:8" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H372" s="22"/>
     </row>
-    <row r="373" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H373" s="22"/>
     </row>
-    <row r="374" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="8:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H374" s="22"/>
     </row>
   </sheetData>
@@ -5192,9 +5242,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D6B7E4-0C50-45F9-82CE-26F41FC338AF}">
   <dimension ref="A1:G309"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>374</v>
       </c>
@@ -5217,7 +5267,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:G11">Context_Input!A4:G13</f>
         <v>#Reactor</v>
@@ -5241,7 +5291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <v>#Reactor</v>
       </c>
@@ -5264,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <v>#Reactor</v>
       </c>
@@ -5287,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <v>#Reactor</v>
       </c>
@@ -5310,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0</v>
       </c>
@@ -5333,7 +5383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
@@ -5356,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0</v>
       </c>
@@ -5379,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0</v>
       </c>
@@ -5402,7 +5452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0</v>
       </c>
@@ -5425,7 +5475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0</v>
       </c>
@@ -5448,7 +5498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="str" cm="1">
         <f t="array" ref="A12:G22">Context_Input!A16:G26</f>
         <v>#Vessel</v>
@@ -5472,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <v>#Vessel</v>
       </c>
@@ -5495,7 +5545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0</v>
       </c>
@@ -5518,7 +5568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0</v>
       </c>
@@ -5541,7 +5591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0</v>
       </c>
@@ -5564,7 +5614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -5587,7 +5637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0</v>
       </c>
@@ -5610,7 +5660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0</v>
       </c>
@@ -5633,7 +5683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0</v>
       </c>
@@ -5656,7 +5706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0</v>
       </c>
@@ -5679,7 +5729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0</v>
       </c>
@@ -5702,7 +5752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="str" cm="1">
         <f t="array" ref="A23:G33">Context_Input!A29:G39</f>
         <v>#Stirrer</v>
@@ -5726,7 +5776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <v>#Stirrer</v>
       </c>
@@ -5749,7 +5799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0</v>
       </c>
@@ -5772,7 +5822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0</v>
       </c>
@@ -5795,7 +5845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0</v>
       </c>
@@ -5818,7 +5868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0</v>
       </c>
@@ -5841,7 +5891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0</v>
       </c>
@@ -5864,7 +5914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0</v>
       </c>
@@ -5887,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0</v>
       </c>
@@ -5910,7 +5960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0</v>
       </c>
@@ -5933,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0</v>
       </c>
@@ -5956,7 +6006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="str" cm="1">
         <f t="array" ref="A34:G44">Context_Input!A42:G52</f>
         <v>#Sparger</v>
@@ -5980,7 +6030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <v>#Sparger</v>
       </c>
@@ -6003,7 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0</v>
       </c>
@@ -6026,7 +6076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0</v>
       </c>
@@ -6049,7 +6099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0</v>
       </c>
@@ -6072,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0</v>
       </c>
@@ -6095,7 +6145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0</v>
       </c>
@@ -6118,7 +6168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0</v>
       </c>
@@ -6141,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0</v>
       </c>
@@ -6164,7 +6214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0</v>
       </c>
@@ -6187,7 +6237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0</v>
       </c>
@@ -6210,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="str" cm="1">
         <f t="array" ref="A45:G55">Context_Input!A55:G65</f>
         <v>#Jacket</v>
@@ -6234,7 +6284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <v>#Jacket</v>
       </c>
@@ -6257,7 +6307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0</v>
       </c>
@@ -6280,7 +6330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0</v>
       </c>
@@ -6303,7 +6353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0</v>
       </c>
@@ -6326,7 +6376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0</v>
       </c>
@@ -6349,7 +6399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0</v>
       </c>
@@ -6372,7 +6422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0</v>
       </c>
@@ -6395,7 +6445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0</v>
       </c>
@@ -6418,7 +6468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0</v>
       </c>
@@ -6441,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0</v>
       </c>
@@ -6464,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="str" cm="1">
         <f t="array" ref="A56:G66">Context_Input!A68:G78</f>
         <v>#TemperatureSensor</v>
@@ -6488,7 +6538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <v>#TemperatureSensor</v>
       </c>
@@ -6511,7 +6561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0</v>
       </c>
@@ -6534,7 +6584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0</v>
       </c>
@@ -6557,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0</v>
       </c>
@@ -6580,7 +6630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>0</v>
       </c>
@@ -6603,7 +6653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>0</v>
       </c>
@@ -6626,7 +6676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>0</v>
       </c>
@@ -6649,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>0</v>
       </c>
@@ -6672,7 +6722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>0</v>
       </c>
@@ -6695,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>0</v>
       </c>
@@ -6718,7 +6768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="str" cm="1">
         <f t="array" ref="A67:G77">Context_Input!A81:G91</f>
         <v>#PressureSensor</v>
@@ -6742,7 +6792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <v>#PressureSensor</v>
       </c>
@@ -6765,7 +6815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>0</v>
       </c>
@@ -6788,7 +6838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>0</v>
       </c>
@@ -6811,7 +6861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>0</v>
       </c>
@@ -6834,7 +6884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>0</v>
       </c>
@@ -6857,7 +6907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>0</v>
       </c>
@@ -6880,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>0</v>
       </c>
@@ -6903,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>0</v>
       </c>
@@ -6926,7 +6976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>0</v>
       </c>
@@ -6949,7 +6999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>0</v>
       </c>
@@ -6972,7 +7022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="str" cm="1">
         <f t="array" ref="A78:G88">Context_Input!A94:G104</f>
         <v>#MassFlowMeter</v>
@@ -6996,7 +7046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <v>#MassFlowMeter</v>
       </c>
@@ -7019,7 +7069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>0</v>
       </c>
@@ -7042,7 +7092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>0</v>
       </c>
@@ -7065,7 +7115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>0</v>
       </c>
@@ -7088,7 +7138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>0</v>
       </c>
@@ -7111,7 +7161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>0</v>
       </c>
@@ -7134,7 +7184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>0</v>
       </c>
@@ -7157,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>0</v>
       </c>
@@ -7180,7 +7230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>0</v>
       </c>
@@ -7203,7 +7253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>0</v>
       </c>
@@ -7226,7 +7276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="str" cm="1">
         <f t="array" ref="A89:G100">Context_Input!A107:G118</f>
         <v>#Balance</v>
@@ -7234,8 +7284,8 @@
       <c r="B89" t="str">
         <v>#LastUsedPurpose_Balance_BeforeFirstUse</v>
       </c>
-      <c r="C89">
-        <v>0</v>
+      <c r="C89" t="str">
+        <v>#StartMassRDY</v>
       </c>
       <c r="D89" t="str">
         <v>#LastUsedTime_Balance</v>
@@ -7250,15 +7300,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="str">
         <v>#Balance</v>
       </c>
       <c r="B90" t="str">
         <v>#DigitalObjectID_Balance</v>
       </c>
-      <c r="C90">
-        <v>0</v>
+      <c r="C90" t="str">
+        <v>#FinalMass_RDY</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -7273,15 +7323,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>0</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
-      <c r="C91">
-        <v>0</v>
+      <c r="C91" t="str">
+        <v>#FinalMass_RDEt</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -7296,15 +7346,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>0</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
-      <c r="C92">
-        <v>0</v>
+      <c r="C92" t="str">
+        <v>#FinalMass_Dimer</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -7319,7 +7369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>0</v>
       </c>
@@ -7342,7 +7392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>0</v>
       </c>
@@ -7365,7 +7415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>0</v>
       </c>
@@ -7388,7 +7438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>0</v>
       </c>
@@ -7411,7 +7461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>0</v>
       </c>
@@ -7434,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>0</v>
       </c>
@@ -7457,7 +7507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>0</v>
       </c>
@@ -7480,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>0</v>
       </c>
@@ -7503,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="str" cm="1">
         <f t="array" ref="A101:G111">Context_Input!A124:G134</f>
         <v>#LiquidPhase</v>
@@ -7527,7 +7577,7 @@
         <v>#InitialMassFraction_Solvent_LiquidPhase</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="str">
         <v>#LiquidPhase</v>
       </c>
@@ -7550,7 +7600,7 @@
         <v>#InitialMassFraction_Water_LiquidPhase</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="str">
         <v>#LiquidPhase</v>
       </c>
@@ -7569,11 +7619,11 @@
       <c r="F103">
         <v>0</v>
       </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G103" t="str">
+        <v>#Reaction1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="str">
         <v>#LiquidPhase</v>
       </c>
@@ -7592,11 +7642,11 @@
       <c r="F104">
         <v>0</v>
       </c>
-      <c r="G104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G104" t="str">
+        <v>#Reaction2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>0</v>
       </c>
@@ -7615,11 +7665,11 @@
       <c r="F105">
         <v>0</v>
       </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G105" t="str">
+        <v>#Reaction3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>0</v>
       </c>
@@ -7642,7 +7692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>0</v>
       </c>
@@ -7665,7 +7715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>0</v>
       </c>
@@ -7688,7 +7738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>0</v>
       </c>
@@ -7711,7 +7761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>0</v>
       </c>
@@ -7734,7 +7784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>0</v>
       </c>
@@ -7757,7 +7807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="str" cm="1">
         <f t="array" ref="A112:G122">Context_Input!A137:G147</f>
         <v>#SolidPhase</v>
@@ -7781,7 +7831,7 @@
         <v>#RDY_Energy</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="str">
         <v>#SolidPhase</v>
       </c>
@@ -7800,11 +7850,11 @@
       <c r="F113">
         <v>0</v>
       </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G113" t="str">
+        <v>#Reaction1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="str">
         <v>#SolidPhase</v>
       </c>
@@ -7827,7 +7877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>0</v>
       </c>
@@ -7850,7 +7900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>0</v>
       </c>
@@ -7873,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>0</v>
       </c>
@@ -7896,7 +7946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>0</v>
       </c>
@@ -7919,7 +7969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>0</v>
       </c>
@@ -7942,7 +7992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>0</v>
       </c>
@@ -7965,7 +8015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>0</v>
       </c>
@@ -7988,7 +8038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>0</v>
       </c>
@@ -8011,7 +8061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="str" cm="1">
         <f t="array" ref="A123:G133">Context_Input!A150:G160</f>
         <v>#CatalystPhase</v>
@@ -8031,11 +8081,11 @@
       <c r="F123">
         <v>0</v>
       </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G123" t="str">
+        <v>#Reaction1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="str">
         <v>#CatalystPhase</v>
       </c>
@@ -8054,11 +8104,11 @@
       <c r="F124">
         <v>0</v>
       </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G124" t="str">
+        <v>#Reaction2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="str">
         <v>#CatalystPhase</v>
       </c>
@@ -8077,11 +8127,11 @@
       <c r="F125">
         <v>0</v>
       </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G125" t="str">
+        <v>#Reaction3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>0</v>
       </c>
@@ -8104,7 +8154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>0</v>
       </c>
@@ -8127,7 +8177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>0</v>
       </c>
@@ -8150,7 +8200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>0</v>
       </c>
@@ -8173,7 +8223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>0</v>
       </c>
@@ -8196,7 +8246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>0</v>
       </c>
@@ -8219,7 +8269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>0</v>
       </c>
@@ -8242,7 +8292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>0</v>
       </c>
@@ -8265,7 +8315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="str" cm="1">
         <f t="array" ref="A134:G144">Context_Input!A163:G173</f>
         <v>#GasPhase</v>
@@ -8289,7 +8339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="str">
         <v>#GasPhase</v>
       </c>
@@ -8312,7 +8362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <v>#GasPhase</v>
       </c>
@@ -8335,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>0</v>
       </c>
@@ -8358,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>0</v>
       </c>
@@ -8381,7 +8431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>0</v>
       </c>
@@ -8404,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>0</v>
       </c>
@@ -8427,7 +8477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>0</v>
       </c>
@@ -8450,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>0</v>
       </c>
@@ -8473,7 +8523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>0</v>
       </c>
@@ -8496,7 +8546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>0</v>
       </c>
@@ -8519,7 +8569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="str" cm="1">
         <f t="array" ref="A145:G155">Context_Input!A176:G186</f>
         <v>#DispersedGasPhase</v>
@@ -8539,11 +8589,11 @@
       <c r="F145">
         <v>0</v>
       </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G145" t="str">
+        <v>#Reaction1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <v>#DispersedGasPhase</v>
       </c>
@@ -8566,7 +8616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <v>#DispersedGasPhase</v>
       </c>
@@ -8589,7 +8639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>0</v>
       </c>
@@ -8612,7 +8662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>0</v>
       </c>
@@ -8635,7 +8685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>0</v>
       </c>
@@ -8658,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>0</v>
       </c>
@@ -8681,7 +8731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>0</v>
       </c>
@@ -8704,7 +8754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>0</v>
       </c>
@@ -8727,7 +8777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>0</v>
       </c>
@@ -8750,7 +8800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>0</v>
       </c>
@@ -8773,7 +8823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="str" cm="1">
         <f t="array" ref="A156:G166">Context_Input!A189:G199</f>
         <v>#CoolingFluidPhase</v>
@@ -8797,7 +8847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="str">
         <v>#CoolingFluidPhase</v>
       </c>
@@ -8820,7 +8870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="str">
         <v>#CoolingFluidPhase</v>
       </c>
@@ -8843,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>0</v>
       </c>
@@ -8866,7 +8916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>0</v>
       </c>
@@ -8889,7 +8939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>0</v>
       </c>
@@ -8912,7 +8962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>0</v>
       </c>
@@ -8935,7 +8985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>0</v>
       </c>
@@ -8958,7 +9008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>0</v>
       </c>
@@ -8981,7 +9031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>0</v>
       </c>
@@ -9004,7 +9054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>0</v>
       </c>
@@ -9027,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="str" cm="1">
         <f t="array" ref="A167:G177">Context_Input!A202:G212</f>
         <v>#HydrogenSpargerPhase</v>
@@ -9051,7 +9101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="str">
         <v>#HydrogenSpargerPhase</v>
       </c>
@@ -9074,7 +9124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="str">
         <v>#HydrogenSpargerPhase</v>
       </c>
@@ -9097,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>0</v>
       </c>
@@ -9120,7 +9170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>0</v>
       </c>
@@ -9143,7 +9193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>0</v>
       </c>
@@ -9166,7 +9216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>0</v>
       </c>
@@ -9189,7 +9239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>0</v>
       </c>
@@ -9212,7 +9262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>0</v>
       </c>
@@ -9235,7 +9285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>0</v>
       </c>
@@ -9258,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>0</v>
       </c>
@@ -9281,7 +9331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="str" cm="1">
         <f t="array" ref="A178:G188">Context_Input!A215:G225</f>
         <v>#CleaningFluidPhase</v>
@@ -9305,7 +9355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>0</v>
       </c>
@@ -9328,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>0</v>
       </c>
@@ -9351,7 +9401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>0</v>
       </c>
@@ -9374,7 +9424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>0</v>
       </c>
@@ -9397,7 +9447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>0</v>
       </c>
@@ -9420,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>0</v>
       </c>
@@ -9443,7 +9493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>0</v>
       </c>
@@ -9466,7 +9516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>0</v>
       </c>
@@ -9489,7 +9539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>0</v>
       </c>
@@ -9512,7 +9562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>0</v>
       </c>
@@ -9535,7 +9585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="str" cm="1">
         <f t="array" ref="A189:G199">Context_Input!A231:G241</f>
         <v>#H2</v>
@@ -9559,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="str">
         <v>#H2</v>
       </c>
@@ -9582,7 +9632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="str">
         <v>#H2</v>
       </c>
@@ -9605,7 +9655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>0</v>
       </c>
@@ -9628,7 +9678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>0</v>
       </c>
@@ -9651,7 +9701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>0</v>
       </c>
@@ -9674,7 +9724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>0</v>
       </c>
@@ -9697,7 +9747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>0</v>
       </c>
@@ -9720,7 +9770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>0</v>
       </c>
@@ -9743,7 +9793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>0</v>
       </c>
@@ -9766,7 +9816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>0</v>
       </c>
@@ -9789,7 +9839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="str" cm="1">
         <f t="array" ref="A200:G210">Context_Input!A244:G254</f>
         <v>#H2O</v>
@@ -9813,7 +9863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>0</v>
       </c>
@@ -9836,7 +9886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>0</v>
       </c>
@@ -9859,7 +9909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>0</v>
       </c>
@@ -9882,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>0</v>
       </c>
@@ -9905,7 +9955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>0</v>
       </c>
@@ -9928,7 +9978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>0</v>
       </c>
@@ -9951,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>0</v>
       </c>
@@ -9974,7 +10024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>0</v>
       </c>
@@ -9997,7 +10047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>0</v>
       </c>
@@ -10020,7 +10070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>0</v>
       </c>
@@ -10043,7 +10093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="str" cm="1">
         <f t="array" ref="A211:G221">Context_Input!A257:G267</f>
         <v>#Solvent</v>
@@ -10067,7 +10117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>0</v>
       </c>
@@ -10090,7 +10140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>0</v>
       </c>
@@ -10113,7 +10163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>0</v>
       </c>
@@ -10136,7 +10186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>0</v>
       </c>
@@ -10159,7 +10209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>0</v>
       </c>
@@ -10182,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>0</v>
       </c>
@@ -10205,7 +10255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>0</v>
       </c>
@@ -10228,7 +10278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>0</v>
       </c>
@@ -10251,7 +10301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>0</v>
       </c>
@@ -10274,7 +10324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>0</v>
       </c>
@@ -10297,7 +10347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="str" cm="1">
         <f t="array" ref="A222:G232">Context_Input!A270:G280</f>
         <v>#RDY</v>
@@ -10321,7 +10371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="str">
         <v>#RDY</v>
       </c>
@@ -10344,7 +10394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="str">
         <v>#RDY</v>
       </c>
@@ -10367,7 +10417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>0</v>
       </c>
@@ -10390,7 +10440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>0</v>
       </c>
@@ -10413,7 +10463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>0</v>
       </c>
@@ -10436,7 +10486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>0</v>
       </c>
@@ -10459,7 +10509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>0</v>
       </c>
@@ -10482,7 +10532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>0</v>
       </c>
@@ -10505,7 +10555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>0</v>
       </c>
@@ -10528,7 +10578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>0</v>
       </c>
@@ -10551,7 +10601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" cm="1">
         <f t="array" ref="A233:G243">Context_Input!A283:G293</f>
         <v>0</v>
@@ -10575,7 +10625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>0</v>
       </c>
@@ -10598,7 +10648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>0</v>
       </c>
@@ -10621,7 +10671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>0</v>
       </c>
@@ -10644,7 +10694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>0</v>
       </c>
@@ -10667,7 +10717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>0</v>
       </c>
@@ -10690,7 +10740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>0</v>
       </c>
@@ -10713,7 +10763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>0</v>
       </c>
@@ -10736,7 +10786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>0</v>
       </c>
@@ -10759,7 +10809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>0</v>
       </c>
@@ -10782,7 +10832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>0</v>
       </c>
@@ -10805,7 +10855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" cm="1">
         <f t="array" ref="A244:G254">Context_Input!A296:G306</f>
         <v>0</v>
@@ -10829,7 +10879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>0</v>
       </c>
@@ -10852,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>0</v>
       </c>
@@ -10875,7 +10925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>0</v>
       </c>
@@ -10898,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>0</v>
       </c>
@@ -10921,7 +10971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>0</v>
       </c>
@@ -10944,7 +10994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>0</v>
       </c>
@@ -10967,7 +11017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>0</v>
       </c>
@@ -10990,7 +11040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>0</v>
       </c>
@@ -11013,7 +11063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>0</v>
       </c>
@@ -11036,7 +11086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>0</v>
       </c>
@@ -11059,7 +11109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" cm="1">
         <f t="array" ref="A255:G265">Context_Input!A309:G319</f>
         <v>0</v>
@@ -11083,7 +11133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>0</v>
       </c>
@@ -11106,7 +11156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>0</v>
       </c>
@@ -11129,7 +11179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>0</v>
       </c>
@@ -11152,7 +11202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>0</v>
       </c>
@@ -11175,7 +11225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>0</v>
       </c>
@@ -11198,7 +11248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>0</v>
       </c>
@@ -11221,7 +11271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>0</v>
       </c>
@@ -11244,7 +11294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>0</v>
       </c>
@@ -11267,7 +11317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>0</v>
       </c>
@@ -11290,7 +11340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>0</v>
       </c>
@@ -11313,7 +11363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="str" cm="1">
         <f t="array" ref="A266:G276">Context_Input!A322:G332</f>
         <v>#RDEt</v>
@@ -11337,7 +11387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>0</v>
       </c>
@@ -11360,7 +11410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>0</v>
       </c>
@@ -11383,7 +11433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>0</v>
       </c>
@@ -11406,7 +11456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>0</v>
       </c>
@@ -11429,7 +11479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>0</v>
       </c>
@@ -11452,7 +11502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>0</v>
       </c>
@@ -11475,7 +11525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>0</v>
       </c>
@@ -11498,7 +11548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>0</v>
       </c>
@@ -11521,7 +11571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>0</v>
       </c>
@@ -11544,7 +11594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>0</v>
       </c>
@@ -11567,7 +11617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="str" cm="1">
         <f t="array" ref="A277:G287">Context_Input!A335:G345</f>
         <v>#Dimer1</v>
@@ -11591,7 +11641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>0</v>
       </c>
@@ -11614,7 +11664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>0</v>
       </c>
@@ -11637,7 +11687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>0</v>
       </c>
@@ -11660,7 +11710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>0</v>
       </c>
@@ -11683,7 +11733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>0</v>
       </c>
@@ -11706,7 +11756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>0</v>
       </c>
@@ -11729,7 +11779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>0</v>
       </c>
@@ -11752,7 +11802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>0</v>
       </c>
@@ -11775,7 +11825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>0</v>
       </c>
@@ -11798,7 +11848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>0</v>
       </c>
@@ -11821,7 +11871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" t="str" cm="1">
         <f t="array" ref="A288:G298">Context_Input!A348:G358</f>
         <v>#Dimer2</v>
@@ -11845,7 +11895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>0</v>
       </c>
@@ -11868,7 +11918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>0</v>
       </c>
@@ -11891,7 +11941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>0</v>
       </c>
@@ -11914,7 +11964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>0</v>
       </c>
@@ -11937,7 +11987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>0</v>
       </c>
@@ -11960,7 +12010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>0</v>
       </c>
@@ -11983,7 +12033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>0</v>
       </c>
@@ -12006,7 +12056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>0</v>
       </c>
@@ -12029,7 +12079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>0</v>
       </c>
@@ -12052,7 +12102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>0</v>
       </c>
@@ -12075,7 +12125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" t="str" cm="1">
         <f t="array" ref="A299:G309">Context_Input!A361:G371</f>
         <v>#Pt</v>
@@ -12099,7 +12149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>0</v>
       </c>
@@ -12122,7 +12172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>0</v>
       </c>
@@ -12145,7 +12195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>0</v>
       </c>
@@ -12168,7 +12218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>0</v>
       </c>
@@ -12191,7 +12241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>0</v>
       </c>
@@ -12214,7 +12264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>0</v>
       </c>
@@ -12237,7 +12287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>0</v>
       </c>
@@ -12260,7 +12310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>0</v>
       </c>
@@ -12283,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>0</v>
       </c>
@@ -12306,7 +12356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>0</v>
       </c>
@@ -12337,17 +12387,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A707C2C-4F81-45CE-8355-AEA9654420E5}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.33203125" customWidth="1"/>
-    <col min="2" max="2" width="29.109375" customWidth="1"/>
-    <col min="11" max="11" width="24.109375" customWidth="1"/>
-    <col min="12" max="12" width="17.88671875" customWidth="1"/>
+    <col min="1" max="1" width="38.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="11" max="11" width="24.140625" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>374</v>
       </c>
@@ -12364,7 +12414,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>477</v>
       </c>
@@ -12375,7 +12425,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>474</v>
       </c>
@@ -12388,13 +12438,13 @@
       <c r="K4" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="s">
         <v>471</v>
@@ -12412,7 +12462,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>407</v>
       </c>
@@ -12435,7 +12485,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>459</v>
       </c>
@@ -12458,7 +12508,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>459</v>
       </c>
@@ -12484,7 +12534,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -12501,7 +12551,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>452</v>
       </c>
@@ -12518,7 +12568,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -12532,7 +12582,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>261</v>
       </c>
@@ -12543,7 +12593,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>266</v>
       </c>
@@ -12554,7 +12604,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>297</v>
       </c>
@@ -12577,7 +12627,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>320</v>
       </c>
@@ -12597,7 +12647,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>327</v>
       </c>
@@ -12608,7 +12658,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>282</v>
       </c>
@@ -12625,7 +12675,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>362</v>
       </c>
@@ -12645,7 +12695,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>338</v>
       </c>
@@ -12662,7 +12712,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>346</v>
       </c>
@@ -12679,7 +12729,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>359</v>
       </c>
@@ -12696,7 +12746,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>419</v>
       </c>
@@ -12716,7 +12766,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>415</v>
       </c>
@@ -12724,7 +12774,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>311</v>
       </c>
@@ -12735,7 +12785,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>411</v>
       </c>
@@ -12746,7 +12796,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>403</v>
       </c>
@@ -12757,7 +12807,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>407</v>
       </c>
@@ -12768,7 +12818,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>404</v>
       </c>
@@ -12779,7 +12829,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>401</v>
       </c>
@@ -12787,7 +12837,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>399</v>
       </c>
@@ -12795,7 +12845,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>397</v>
       </c>
@@ -12803,12 +12853,12 @@
         <v>383</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>396</v>
       </c>
@@ -12819,7 +12869,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>394</v>
       </c>
@@ -12830,7 +12880,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>391</v>
       </c>
@@ -12838,7 +12888,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>389</v>
       </c>
@@ -12846,7 +12896,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>387</v>
       </c>
@@ -12857,7 +12907,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>336</v>
       </c>
@@ -12865,7 +12915,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>370</v>
       </c>
@@ -12873,7 +12923,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>342</v>
       </c>
@@ -12881,7 +12931,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>350</v>
       </c>
@@ -12889,7 +12939,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>355</v>
       </c>
@@ -12897,7 +12947,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>335</v>
       </c>
@@ -12905,7 +12955,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>368</v>
       </c>
@@ -12913,7 +12963,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>341</v>
       </c>
@@ -12921,7 +12971,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>349</v>
       </c>
@@ -12929,7 +12979,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>354</v>
       </c>

--- a/CASESTUDY_Hydrogenation.xlsx
+++ b/CASESTUDY_Hydrogenation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/lf576_cam_ac_uk/Documents/04_Coding/hydrogenation/current_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C125219F-38CE-4786-915C-CFB519907254}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF7C0A2E-C8D9-446A-BC72-41ADC02F7BB1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="492">
   <si>
     <t>This is the file containing all the information about the Hydrogenation Process Case Study</t>
   </si>
@@ -831,9 +831,6 @@
   </si>
   <si>
     <t>Dimer1</t>
-  </si>
-  <si>
-    <t>#FinalMassRDEt</t>
   </si>
   <si>
     <t>#RDEt</t>
@@ -2041,27 +2038,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3786,7 +3783,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B1" t="s">
         <v>243</v>
@@ -3807,13 +3804,13 @@
         <v>233</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -3830,74 +3827,74 @@
     </row>
     <row r="4" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" t="s">
         <v>360</v>
       </c>
-      <c r="B6" t="s">
-        <v>363</v>
-      </c>
-      <c r="C6" t="s">
-        <v>362</v>
-      </c>
-      <c r="D6" t="s">
-        <v>361</v>
-      </c>
       <c r="H6" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H8" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H9" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3909,7 +3906,7 @@
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H15" s="18"/>
       <c r="J15" s="2" t="s">
@@ -3918,48 +3915,48 @@
     </row>
     <row r="16" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H18" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H19" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H20" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -3984,61 +3981,61 @@
     </row>
     <row r="29" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C29" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C30" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H31" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H32" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H33" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H34" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H35" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4059,51 +4056,51 @@
     </row>
     <row r="42" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D42" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H44" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H45" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H46" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4126,51 +4123,51 @@
     </row>
     <row r="55" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C55" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D55" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H57" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H58" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H59" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4184,7 +4181,7 @@
     </row>
     <row r="67" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H67" s="18"/>
       <c r="J67" s="2" t="s">
@@ -4193,51 +4190,51 @@
     </row>
     <row r="68" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B69" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C69" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H70" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H71" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H72" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4251,7 +4248,7 @@
     </row>
     <row r="80" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H80" s="18"/>
       <c r="J80" s="2" t="s">
@@ -4260,51 +4257,51 @@
     </row>
     <row r="81" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C81" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D82" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H83" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H84" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H85" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4318,7 +4315,7 @@
     </row>
     <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H93" s="18"/>
       <c r="J93" s="2" t="s">
@@ -4327,54 +4324,54 @@
     </row>
     <row r="94" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B94" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H94" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I94" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B95" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C95" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D95" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H95" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H96" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H97" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H98" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4388,7 +4385,7 @@
     </row>
     <row r="106" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H106" s="18"/>
       <c r="J106" s="2" t="s">
@@ -4397,54 +4394,60 @@
     </row>
     <row r="107" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B107" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C107" t="s">
-        <v>419</v>
+        <v>258</v>
       </c>
       <c r="D107" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H107" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B108" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C108" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H108" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="109" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>307</v>
+      </c>
       <c r="C109" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H109" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="110" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>307</v>
+      </c>
       <c r="C110" t="s">
         <v>250</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="111" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="H111" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4477,57 +4480,60 @@
     </row>
     <row r="124" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E124" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G124" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I124" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E125" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G125" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E126" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G126" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E127" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G127" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>298</v>
+      </c>
+      <c r="G128" t="s">
         <v>491</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="G128" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4550,35 +4556,35 @@
     </row>
     <row r="137" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C137" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E137" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G137" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E138" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G138" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E139" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4603,38 +4609,38 @@
     </row>
     <row r="150" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C150" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E150" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G150" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E151" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G151" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E152" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G152" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4659,29 +4665,29 @@
     </row>
     <row r="163" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C163" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E163" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E164" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E165" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4697,7 +4703,7 @@
     </row>
     <row r="175" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H175" s="20"/>
       <c r="J175" s="13" t="s">
@@ -4706,32 +4712,32 @@
     </row>
     <row r="176" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C176" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E176" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G176" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E177" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E178" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4747,7 +4753,7 @@
     </row>
     <row r="188" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H188" s="20"/>
       <c r="J188" s="13" t="s">
@@ -4756,32 +4762,32 @@
     </row>
     <row r="189" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C189" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E189" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I189" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E190" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E191" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4797,7 +4803,7 @@
     </row>
     <row r="201" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H201" s="20"/>
       <c r="J201" s="13" t="s">
@@ -4806,29 +4812,29 @@
     </row>
     <row r="202" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C202" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E202" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E204" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4844,7 +4850,7 @@
     </row>
     <row r="214" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H214" s="20"/>
       <c r="J214" s="13" t="s">
@@ -4853,7 +4859,7 @@
     </row>
     <row r="215" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4880,7 +4886,7 @@
     </row>
     <row r="230" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H230" s="21"/>
       <c r="J230" s="10" t="s">
@@ -4892,7 +4898,7 @@
         <v>115</v>
       </c>
       <c r="C231" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -4900,7 +4906,7 @@
         <v>115</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -4908,7 +4914,7 @@
         <v>115</v>
       </c>
       <c r="C233" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4933,16 +4939,16 @@
     </row>
     <row r="244" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E244" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I244" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -4960,7 +4966,7 @@
     </row>
     <row r="256" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H256" s="21"/>
       <c r="J256" s="10" t="s">
@@ -4969,16 +4975,16 @@
     </row>
     <row r="257" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C257" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E257" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I257" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -5008,7 +5014,7 @@
         <v>146</v>
       </c>
       <c r="C270" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -5016,7 +5022,7 @@
         <v>146</v>
       </c>
       <c r="C271" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -5024,7 +5030,7 @@
         <v>146</v>
       </c>
       <c r="C272" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="273" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -5086,7 +5092,7 @@
     </row>
     <row r="308" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H308" s="21"/>
       <c r="J308" s="10" t="s">
@@ -5118,10 +5124,10 @@
     </row>
     <row r="322" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C322" t="s">
-        <v>255</v>
+        <v>451</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="14.45" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -5246,7 +5252,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B1" t="s">
         <v>243</v>
@@ -7285,7 +7291,7 @@
         <v>#LastUsedPurpose_Balance_BeforeFirstUse</v>
       </c>
       <c r="C89" t="str">
-        <v>#StartMassRDY</v>
+        <v>#StartMass_RDY</v>
       </c>
       <c r="D89" t="str">
         <v>#LastUsedTime_Balance</v>
@@ -7324,8 +7330,8 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>0</v>
+      <c r="A91" t="str">
+        <v>#Balance</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -7347,8 +7353,8 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>0</v>
+      <c r="A92" t="str">
+        <v>#Balance</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -7647,8 +7653,8 @@
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>0</v>
+      <c r="A105" t="str">
+        <v>#LiquidPhase</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -11372,7 +11378,7 @@
         <v>0</v>
       </c>
       <c r="C266" t="str">
-        <v>#FinalMassRDEt</v>
+        <v>#FinalMass_RDEt</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -12399,47 +12405,47 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
@@ -12447,16 +12453,16 @@
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>90</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q5" t="s">
         <v>243</v>
@@ -12464,22 +12470,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q6" t="s">
         <v>241</v>
@@ -12487,22 +12493,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7" t="s">
+        <v>463</v>
+      </c>
+      <c r="E7" t="s">
+        <v>462</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="L7" t="s">
+        <v>460</v>
+      </c>
+      <c r="M7" t="s">
         <v>459</v>
-      </c>
-      <c r="B7" t="s">
-        <v>464</v>
-      </c>
-      <c r="E7" t="s">
-        <v>463</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="L7" t="s">
-        <v>461</v>
-      </c>
-      <c r="M7" t="s">
-        <v>460</v>
       </c>
       <c r="Q7" t="s">
         <v>239</v>
@@ -12510,25 +12516,25 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q8" t="s">
         <v>237</v>
@@ -12539,13 +12545,13 @@
         <v>250</v>
       </c>
       <c r="B9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q9" t="s">
         <v>235</v>
@@ -12553,16 +12559,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q10" t="s">
         <v>233</v>
@@ -12570,13 +12576,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M11" t="s">
         <v>241</v>
@@ -12584,10 +12590,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>89</v>
@@ -12595,10 +12601,10 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>248</v>
@@ -12606,141 +12612,141 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N15" t="s">
         <v>243</v>
       </c>
       <c r="O15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B18" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E18" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M18" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N18" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B19" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N19" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="O19" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M20" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B21" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M21" t="s">
         <v>233</v>
@@ -12748,19 +12754,19 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B22" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L22" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M22" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N22" t="s">
         <v>239</v>
@@ -12768,223 +12774,223 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B24" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E24" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B25" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E25" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B26" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E26" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B27" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B28" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E28" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B29" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B30" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B31" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E33" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B34" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E34" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E37" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/CASESTUDY_Hydrogenation.xlsx
+++ b/CASESTUDY_Hydrogenation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/lf576_cam_ac_uk/Documents/04_Coding/hydrogenation/current_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF7C0A2E-C8D9-446A-BC72-41ADC02F7BB1}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{3CA0C22B-1C3C-468B-A8A4-EC46740A7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3A68B46-3FC5-4FA3-93A6-BEB0CEDDED5D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{D5389695-9B6E-4686-BC98-C44AC3042CAD}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="494">
   <si>
     <t>This is the file containing all the information about the Hydrogenation Process Case Study</t>
   </si>
@@ -1542,6 +1542,12 @@
   </si>
   <si>
     <t>#Reaction3</t>
+  </si>
+  <si>
+    <t>Wurde nicht eingetragen</t>
+  </si>
+  <si>
+    <t>Vll weil die Beziehung auch in die andere Richtung geht?</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1589,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1638,6 +1644,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1660,7 +1672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1690,6 +1702,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4183,6 +4196,9 @@
       <c r="A67" s="2" t="s">
         <v>331</v>
       </c>
+      <c r="C67" s="2" t="s">
+        <v>493</v>
+      </c>
       <c r="H67" s="18"/>
       <c r="J67" s="2" t="s">
         <v>90</v>
@@ -4195,7 +4211,7 @@
       <c r="B68" t="s">
         <v>329</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="23" t="s">
         <v>314</v>
       </c>
       <c r="D68" s="7" t="s">
@@ -4212,7 +4228,7 @@
       <c r="B69" t="s">
         <v>327</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="23" t="s">
         <v>326</v>
       </c>
       <c r="D69" t="s">
@@ -4250,6 +4266,9 @@
       <c r="A80" s="2" t="s">
         <v>324</v>
       </c>
+      <c r="C80" s="2" t="s">
+        <v>492</v>
+      </c>
       <c r="H80" s="18"/>
       <c r="J80" s="2" t="s">
         <v>90</v>
@@ -4262,7 +4281,7 @@
       <c r="B81" t="s">
         <v>322</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="23" t="s">
         <v>314</v>
       </c>
       <c r="D81" s="7" t="s">
@@ -4279,7 +4298,7 @@
       <c r="B82" t="s">
         <v>320</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="23" t="s">
         <v>319</v>
       </c>
       <c r="D82" t="s">
